--- a/data/output/daf_clean.xlsx
+++ b/data/output/daf_clean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:T68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,85 +367,90 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>salty</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ShortName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>AbottleID</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CbottleID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Li_Ca</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>B_Ca</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Na_Ca</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Mg_Ca</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Mn_Ca</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ni_Ca</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Cu_Ca</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Zn_Ca</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Sr_Ca</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Ba_Ca</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pb_Ca</t>
         </is>
@@ -453,71 +458,76 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cleveland-AlligatorCkFresh</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>-19.388219</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TSV-Bluewater</t>
+        </is>
       </c>
       <c r="E2">
-        <v>146.957034</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>-19.176311</v>
+      </c>
+      <c r="F2">
+        <v>146.552749</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>A74630</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C11004</t>
-        </is>
-      </c>
-      <c r="I2">
-        <v>0.0005813953488372093</v>
+          <t>A83996</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C11768</t>
+        </is>
       </c>
       <c r="J2">
-        <v>0.004418604651162791</v>
+        <v>0.003125</v>
       </c>
       <c r="K2">
-        <v>2.558139534883721</v>
+        <v>0.01125</v>
       </c>
       <c r="L2">
-        <v>0.6511627906976744</v>
+        <v>7.5</v>
       </c>
       <c r="M2">
-        <v>0.005581395348837209</v>
+        <v>0.3125</v>
       </c>
       <c r="N2">
-        <v>0.0001162790697674419</v>
+        <v>0.006875</v>
       </c>
       <c r="O2">
-        <v>2.325581395348837E-05</v>
+        <v>0.000625</v>
       </c>
       <c r="P2">
-        <v>0.004627906976744186</v>
+        <v>0.00025</v>
       </c>
       <c r="Q2">
-        <v>0.009627906976744186</v>
+        <v>0.013</v>
       </c>
       <c r="R2">
-        <v>0.003302325581395349</v>
+        <v>0.004225</v>
       </c>
       <c r="S2">
-        <v>8.13953488372093E-05</v>
+        <v>0.002875</v>
+      </c>
+      <c r="T2">
+        <v>0.0001125</v>
       </c>
     </row>
     <row r="3">
@@ -531,62 +541,67 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Upstart-RMCk</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>-19.869901</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ingham-CattleCk</t>
+        </is>
       </c>
       <c r="E3">
-        <v>147.667908</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>-18.734647</v>
+      </c>
+      <c r="F3">
+        <v>146.14108</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>A77326</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C11005</t>
-        </is>
-      </c>
-      <c r="I3">
-        <v>0.0003472222222222222</v>
+          <t>C12113 (ran out of A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C11009</t>
+        </is>
       </c>
       <c r="J3">
-        <v>0.004027777777777778</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="K3">
-        <v>1.666666666666667</v>
+        <v>0.006666666666666667</v>
       </c>
       <c r="L3">
-        <v>0.4583333333333333</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="M3">
-        <v>0.001208333333333333</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="N3">
-        <v>0.0001666666666666667</v>
+        <v>0.03788888888888889</v>
       </c>
       <c r="O3">
-        <v>0.0004583333333333333</v>
+        <v>0.0002777777777777778</v>
       </c>
       <c r="P3">
-        <v>6.944444444444444E-05</v>
+        <v>0.0006666666666666666</v>
       </c>
       <c r="Q3">
-        <v>0.01430555555555556</v>
+        <v>0.001666666666666667</v>
       </c>
       <c r="R3">
-        <v>0.004958333333333334</v>
+        <v>0.0105</v>
       </c>
       <c r="S3">
-        <v>1.805555555555555E-05</v>
+        <v>0.01255555555555556</v>
+      </c>
+      <c r="T3">
+        <v>0.0001388888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -600,62 +615,67 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ingham-CattleCk</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-18.734647</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TSV-Bohle</t>
+        </is>
       </c>
       <c r="E4">
-        <v>146.14108</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>-19.25816</v>
+      </c>
+      <c r="F4">
+        <v>146.706871</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>C12113 (ran out of A</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C11009</t>
-        </is>
-      </c>
-      <c r="I4">
-        <v>0.001388888888888889</v>
+          <t>A77327</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>C12200</t>
+        </is>
       </c>
       <c r="J4">
-        <v>0.006666666666666667</v>
+        <v>0.00078125</v>
       </c>
       <c r="K4">
-        <v>2.222222222222222</v>
+        <v>0.005</v>
       </c>
       <c r="L4">
-        <v>0.4444444444444445</v>
+        <v>2.1875</v>
       </c>
       <c r="M4">
-        <v>0.03788888888888889</v>
+        <v>0.40625</v>
       </c>
       <c r="N4">
-        <v>0.0002777777777777778</v>
+        <v>0.00309375</v>
       </c>
       <c r="O4">
-        <v>0.0006666666666666666</v>
+        <v>0.00015625</v>
       </c>
       <c r="P4">
-        <v>0.001666666666666667</v>
+        <v>0.00040625</v>
       </c>
       <c r="Q4">
-        <v>0.0105</v>
+        <v>0.0006875000000000001</v>
       </c>
       <c r="R4">
-        <v>0.01255555555555556</v>
+        <v>0.00928125</v>
       </c>
       <c r="S4">
-        <v>0.0001388888888888889</v>
+        <v>0.008375</v>
+      </c>
+      <c r="T4">
+        <v>5.3125E-05</v>
       </c>
     </row>
     <row r="5">
@@ -669,205 +689,220 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ingham-TrebCk</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-18.738313</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ross-dam</t>
+        </is>
       </c>
       <c r="E5">
-        <v>146.198335</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>-19.429937</v>
+      </c>
+      <c r="F5">
+        <v>146.738035</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>A74359</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C11015</t>
-        </is>
-      </c>
-      <c r="I5">
-        <v>0.0005555555555555556</v>
+          <t>A74617</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C11019</t>
+        </is>
       </c>
       <c r="J5">
-        <v>0.003333333333333334</v>
+        <v>0.0005102040816326531</v>
       </c>
       <c r="K5">
-        <v>2.444444444444445</v>
+        <v>0.003061224489795918</v>
       </c>
       <c r="L5">
-        <v>0.4444444444444444</v>
+        <v>1.224489795918367</v>
       </c>
       <c r="M5">
-        <v>0.01193333333333333</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="N5">
-        <v>0.0001111111111111111</v>
+        <v>0.0005714285714285714</v>
       </c>
       <c r="O5">
-        <v>0.0001333333333333333</v>
+        <v>0.0001020408163265306</v>
       </c>
       <c r="P5">
-        <v>0.0003777777777777778</v>
+        <v>0.0001020408163265306</v>
       </c>
       <c r="Q5">
-        <v>0.008977777777777777</v>
+        <v>0.001224489795918367</v>
       </c>
       <c r="R5">
-        <v>0.005977777777777777</v>
+        <v>0.009081632653061224</v>
       </c>
       <c r="S5">
-        <v>4.666666666666666E-05</v>
+        <v>0.004551020408163266</v>
+      </c>
+      <c r="T5">
+        <v>3.469387755102041E-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ross-dam</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-19.429937</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Upstart-CapeCk</t>
+        </is>
       </c>
       <c r="E6">
-        <v>146.738035</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>-19.902055</v>
+      </c>
+      <c r="F6">
+        <v>147.75906</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>A74617</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C11019</t>
-        </is>
-      </c>
-      <c r="I6">
-        <v>0.0005102040816326531</v>
+          <t>A77321</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C11142</t>
+        </is>
       </c>
       <c r="J6">
-        <v>0.003061224489795918</v>
+        <v>0.0004545454545454545</v>
       </c>
       <c r="K6">
-        <v>1.224489795918367</v>
+        <v>0.007272727272727273</v>
       </c>
       <c r="L6">
-        <v>0.3877551020408163</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="M6">
-        <v>0.0005714285714285714</v>
+        <v>0.4363636363636363</v>
       </c>
       <c r="N6">
-        <v>0.0001020408163265306</v>
+        <v>0.002436363636363636</v>
       </c>
       <c r="O6">
-        <v>0.0001020408163265306</v>
+        <v>9.09090909090909E-05</v>
       </c>
       <c r="P6">
-        <v>0.001224489795918367</v>
+        <v>0.0003272727272727273</v>
       </c>
       <c r="Q6">
-        <v>0.009081632653061224</v>
+        <v>0.0005454545454545455</v>
       </c>
       <c r="R6">
-        <v>0.004551020408163266</v>
+        <v>0.01265454545454545</v>
       </c>
       <c r="S6">
-        <v>3.469387755102041E-05</v>
+        <v>0.008</v>
+      </c>
+      <c r="T6">
+        <v>2.727272727272727E-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Burd-Barrattas</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-19.56949</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ingham-CattleCk</t>
+        </is>
       </c>
       <c r="E7">
-        <v>147.222052</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-18.714525</v>
+      </c>
+      <c r="F7">
+        <v>146.108619</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A75501</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C11027</t>
-        </is>
-      </c>
-      <c r="I7">
-        <v>0.0002976190476190476</v>
+          <t>A74837</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>C11108</t>
+        </is>
       </c>
       <c r="J7">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="K7">
-        <v>2.619047619047619</v>
+        <v>0.006</v>
       </c>
       <c r="L7">
-        <v>0.488095238095238</v>
+        <v>5.2</v>
       </c>
       <c r="M7">
-        <v>0.0009285714285714286</v>
+        <v>0.6</v>
       </c>
       <c r="N7">
-        <v>5.952380952380952E-05</v>
+        <v>0.01304</v>
       </c>
       <c r="O7">
-        <v>0.0002380952380952381</v>
+        <v>0.0002</v>
       </c>
       <c r="P7">
-        <v>0.004119047619047619</v>
+        <v>0.00024</v>
       </c>
       <c r="Q7">
-        <v>0.01057142857142857</v>
+        <v>0.0005200000000000001</v>
       </c>
       <c r="R7">
-        <v>0.005333333333333333</v>
+        <v>0.00776</v>
       </c>
       <c r="S7">
-        <v>8.333333333333334E-06</v>
+        <v>0.006959999999999999</v>
+      </c>
+      <c r="T7">
+        <v>0.00012</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -876,67 +911,72 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Haught-Heatleys</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-19.516906</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ross-dam</t>
+        </is>
       </c>
       <c r="E8">
-        <v>147.045995</v>
-      </c>
-      <c r="F8" t="inlineStr">
+        <v>-19.429937</v>
+      </c>
+      <c r="F8">
+        <v>146.738035</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>A74697</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C11042</t>
-        </is>
-      </c>
-      <c r="I8">
-        <v>3.586800573888092E-05</v>
+          <t>A74828</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C12193</t>
+        </is>
       </c>
       <c r="J8">
-        <v>0.002159090909090909</v>
+        <v>0.0004464285714285714</v>
       </c>
       <c r="K8">
-        <v>1.988636363636364</v>
+        <v>0.0025</v>
       </c>
       <c r="L8">
-        <v>0.5454545454545454</v>
+        <v>1.607142857142857</v>
       </c>
       <c r="M8">
-        <v>3.409090909090909E-05</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="N8">
-        <v>2.840909090909091E-05</v>
+        <v>0.0006428571428571428</v>
       </c>
       <c r="O8">
-        <v>5.681818181818182E-06</v>
+        <v>8.928571428571429E-05</v>
       </c>
       <c r="P8">
-        <v>0.0001534090909090909</v>
+        <v>8.928571428571429E-05</v>
       </c>
       <c r="Q8">
-        <v>0.008750000000000001</v>
+        <v>8.928571428571429E-05</v>
       </c>
       <c r="R8">
-        <v>0.002818181818181818</v>
+        <v>0.006339285714285714</v>
       </c>
       <c r="S8">
-        <v>1.420454545454546E-06</v>
+        <v>0.003589285714285715</v>
+      </c>
+      <c r="T8">
+        <v>4.464285714285715E-06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -945,131 +985,141 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Upstart-CapeCk</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-19.902055</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TSV-BlackRiver</t>
+        </is>
       </c>
       <c r="E9">
-        <v>147.75906</v>
-      </c>
-      <c r="F9" t="inlineStr">
+        <v>-19.227514</v>
+      </c>
+      <c r="F9">
+        <v>146.629221</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>A74626</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C11050</t>
-        </is>
-      </c>
-      <c r="I9">
-        <v>6.811989100817439E-05</v>
+          <t>A83987</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C11055</t>
+        </is>
       </c>
       <c r="J9">
-        <v>0.001525885558583106</v>
+        <v>0.0004310344827586207</v>
       </c>
       <c r="K9">
-        <v>2.343324250681199</v>
+        <v>0.0005172413793103448</v>
       </c>
       <c r="L9">
-        <v>0.4223433242506812</v>
+        <v>1.379310344827586</v>
       </c>
       <c r="M9">
-        <v>0.00662125340599455</v>
+        <v>0.3275862068965517</v>
       </c>
       <c r="N9">
-        <v>2.724795640326975E-05</v>
+        <v>0.000603448275862069</v>
       </c>
       <c r="O9">
-        <v>1.907356948228883E-05</v>
+        <v>0.0002413793103448276</v>
       </c>
       <c r="P9">
-        <v>8.991825613079019E-05</v>
+        <v>0.0001896551724137931</v>
       </c>
       <c r="Q9">
-        <v>0.01040871934604905</v>
+        <v>0.0002586206896551724</v>
       </c>
       <c r="R9">
-        <v>0.004713896457765668</v>
+        <v>0.004810344827586206</v>
       </c>
       <c r="S9">
-        <v>9.209809264305177E-05</v>
+        <v>0.003655172413793103</v>
+      </c>
+      <c r="T9">
+        <v>1.551724137931035E-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TSV-BlackRiver</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>-19.227514</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cleveland-AlligatorCkFresh</t>
+        </is>
       </c>
       <c r="E10">
-        <v>146.629221</v>
-      </c>
-      <c r="F10" t="inlineStr">
+        <v>-19.388219</v>
+      </c>
+      <c r="F10">
+        <v>146.957034</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>A83987</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C11055</t>
-        </is>
-      </c>
-      <c r="I10">
-        <v>0.0004310344827586207</v>
+          <t>A74630</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C11004</t>
+        </is>
       </c>
       <c r="J10">
-        <v>0.0005172413793103448</v>
+        <v>0.0005813953488372093</v>
       </c>
       <c r="K10">
-        <v>1.379310344827586</v>
+        <v>0.004418604651162791</v>
       </c>
       <c r="L10">
-        <v>0.3275862068965517</v>
+        <v>2.558139534883721</v>
       </c>
       <c r="M10">
-        <v>0.000603448275862069</v>
+        <v>0.6511627906976744</v>
       </c>
       <c r="N10">
-        <v>0.0002413793103448276</v>
+        <v>0.005581395348837209</v>
       </c>
       <c r="O10">
-        <v>0.0001896551724137931</v>
+        <v>0.0001162790697674419</v>
       </c>
       <c r="P10">
-        <v>0.0002586206896551724</v>
+        <v>2.325581395348837E-05</v>
       </c>
       <c r="Q10">
-        <v>0.004810344827586206</v>
+        <v>0.004627906976744186</v>
       </c>
       <c r="R10">
-        <v>0.003655172413793103</v>
+        <v>0.009627906976744186</v>
       </c>
       <c r="S10">
-        <v>1.551724137931035E-05</v>
+        <v>0.003302325581395349</v>
+      </c>
+      <c r="T10">
+        <v>8.13953488372093E-05</v>
       </c>
     </row>
     <row r="11">
@@ -1078,210 +1128,225 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burd-Anabran</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-19.625405</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ingham-TrebCk</t>
+        </is>
       </c>
       <c r="E11">
-        <v>147.482742</v>
-      </c>
-      <c r="F11" t="inlineStr">
+        <v>-18.738313</v>
+      </c>
+      <c r="F11">
+        <v>146.198335</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>A74636</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C11057</t>
-        </is>
-      </c>
-      <c r="I11">
-        <v>0.0003246753246753247</v>
+          <t>A74359</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>C11015</t>
+        </is>
       </c>
       <c r="J11">
-        <v>0.003116883116883117</v>
+        <v>0.0005555555555555556</v>
       </c>
       <c r="K11">
-        <v>1.298701298701299</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="L11">
-        <v>0.5064935064935064</v>
+        <v>2.444444444444445</v>
       </c>
       <c r="M11">
-        <v>0.001207792207792208</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N11">
-        <v>6.493506493506494E-05</v>
+        <v>0.01193333333333333</v>
       </c>
       <c r="O11">
-        <v>0.0001948051948051948</v>
+        <v>0.0001111111111111111</v>
       </c>
       <c r="P11">
-        <v>0.0002337662337662338</v>
+        <v>0.0001333333333333333</v>
       </c>
       <c r="Q11">
-        <v>0.008311688311688312</v>
+        <v>0.0003777777777777778</v>
       </c>
       <c r="R11">
-        <v>0.003337662337662338</v>
+        <v>0.008977777777777777</v>
       </c>
       <c r="S11">
-        <v>4.155844155844156E-05</v>
+        <v>0.005977777777777777</v>
+      </c>
+      <c r="T11">
+        <v>4.666666666666666E-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ross-Gleesons</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>-19.315906</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ross-Aplins</t>
+        </is>
       </c>
       <c r="E12">
-        <v>146.736257</v>
-      </c>
-      <c r="F12" t="inlineStr">
+        <v>-19.30468</v>
+      </c>
+      <c r="F12">
+        <v>146.781019</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>A83989</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C11058</t>
-        </is>
-      </c>
-      <c r="I12">
-        <v>0.0002336448598130841</v>
+          <t>A74629</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>C11114</t>
+        </is>
       </c>
       <c r="J12">
-        <v>0.002523364485981308</v>
+        <v>0.0003623188405797101</v>
       </c>
       <c r="K12">
-        <v>2.05607476635514</v>
+        <v>0.002463768115942029</v>
       </c>
       <c r="L12">
-        <v>0.4672897196261683</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="M12">
-        <v>0.0006542056074766356</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="N12">
-        <v>4.672897196261682E-05</v>
+        <v>0.0004347826086956522</v>
       </c>
       <c r="O12">
-        <v>4.672897196261682E-05</v>
+        <v>7.246376811594203E-05</v>
       </c>
       <c r="P12">
-        <v>0.0001214953271028037</v>
+        <v>0.0001449275362318841</v>
       </c>
       <c r="Q12">
-        <v>0.008542056074766356</v>
+        <v>0.001043478260869565</v>
       </c>
       <c r="R12">
-        <v>0.004289719626168224</v>
+        <v>0.008869565217391304</v>
       </c>
       <c r="S12">
-        <v>2.336448598130841E-06</v>
+        <v>0.004565217391304348</v>
+      </c>
+      <c r="T12">
+        <v>3.623188405797101E-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Haught-mouth</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>-19.411312</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Burd-Anabran</t>
+        </is>
       </c>
       <c r="E13">
-        <v>147.116264</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.625405</v>
+      </c>
+      <c r="F13">
+        <v>147.482742</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A74702</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C11061</t>
-        </is>
-      </c>
-      <c r="I13">
-        <v>3.586800573888092E-05</v>
+          <t>A74636</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C11057</t>
+        </is>
       </c>
       <c r="J13">
-        <v>0.009782135076252724</v>
+        <v>0.0003246753246753247</v>
       </c>
       <c r="K13">
-        <v>23.31154684095861</v>
+        <v>0.003116883116883117</v>
       </c>
       <c r="L13">
-        <v>3.18082788671024</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="M13">
-        <v>1.982570806100218E-05</v>
+        <v>0.5064935064935064</v>
       </c>
       <c r="N13">
-        <v>1.089324618736383E-05</v>
+        <v>0.001207792207792208</v>
       </c>
       <c r="O13">
-        <v>2.178649237472767E-06</v>
+        <v>6.493506493506494E-05</v>
       </c>
       <c r="P13">
-        <v>8.278867102396513E-06</v>
+        <v>0.0001948051948051948</v>
       </c>
       <c r="Q13">
-        <v>0.002830188679245283</v>
+        <v>0.0002337662337662338</v>
       </c>
       <c r="R13">
-        <v>1.655773420479303E-05</v>
+        <v>0.008311688311688312</v>
       </c>
       <c r="S13">
-        <v>8.278867102396515E-07</v>
+        <v>0.003337662337662338</v>
+      </c>
+      <c r="T13">
+        <v>4.155844155844156E-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1290,343 +1355,368 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ross-mouth</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>-19.275335</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Haught-Giru</t>
+        </is>
       </c>
       <c r="E14">
-        <v>146.830675</v>
-      </c>
-      <c r="F14" t="inlineStr">
+        <v>-19.512679</v>
+      </c>
+      <c r="F14">
+        <v>147.112332</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>A74620</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C11066</t>
-        </is>
-      </c>
-      <c r="I14">
-        <v>0.0002681159420289855</v>
+          <t>A83986</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>C11745</t>
+        </is>
       </c>
       <c r="J14">
-        <v>0.009094202898550724</v>
+        <v>0.0004464285714285714</v>
       </c>
       <c r="K14">
-        <v>23.80434782608696</v>
+        <v>0.004464285714285714</v>
       </c>
       <c r="L14">
-        <v>3.097826086956522</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="M14">
-        <v>0.000133695652173913</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="N14">
-        <v>1.811594202898551E-05</v>
+        <v>0.001696428571428571</v>
       </c>
       <c r="O14">
-        <v>3.623188405797101E-06</v>
+        <v>8.928571428571429E-05</v>
       </c>
       <c r="P14">
-        <v>7.173913043478262E-05</v>
+        <v>0.0002321428571428571</v>
       </c>
       <c r="Q14">
-        <v>0.01681159420289855</v>
+        <v>0.003392857142857143</v>
       </c>
       <c r="R14">
-        <v>0.000394927536231884</v>
+        <v>0.009232142857142857</v>
       </c>
       <c r="S14">
-        <v>0.0003985507246376811</v>
+        <v>0.004928571428571429</v>
+      </c>
+      <c r="T14">
+        <v>1.071428571428571E-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ross-Aplins</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>-19.30468</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Upstart-RMCk</t>
+        </is>
       </c>
       <c r="E15">
-        <v>146.781019</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.869901</v>
+      </c>
+      <c r="F15">
+        <v>147.667908</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A74684</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C11074</t>
-        </is>
-      </c>
-      <c r="I15">
-        <v>3.586800573888092E-05</v>
+          <t>A77326</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>C11005</t>
+        </is>
       </c>
       <c r="J15">
-        <v>0.001608040201005025</v>
+        <v>0.0003472222222222222</v>
       </c>
       <c r="K15">
-        <v>1.85929648241206</v>
+        <v>0.004027777777777778</v>
       </c>
       <c r="L15">
-        <v>0.4673366834170855</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="M15">
-        <v>0.0001206030150753769</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N15">
-        <v>2.512562814070352E-05</v>
+        <v>0.001208333333333333</v>
       </c>
       <c r="O15">
-        <v>2.010050251256282E-05</v>
+        <v>0.0001666666666666667</v>
       </c>
       <c r="P15">
-        <v>0.0001105527638190955</v>
+        <v>0.0004583333333333333</v>
       </c>
       <c r="Q15">
-        <v>0.006834170854271356</v>
+        <v>6.944444444444444E-05</v>
       </c>
       <c r="R15">
-        <v>0.002688442211055276</v>
+        <v>0.01430555555555556</v>
       </c>
       <c r="S15">
-        <v>1.256281407035176E-06</v>
+        <v>0.004958333333333334</v>
+      </c>
+      <c r="T15">
+        <v>1.805555555555555E-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Haught-BarraCk</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>-19.479586</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ross-dam</t>
+        </is>
       </c>
       <c r="E16">
-        <v>147.150848</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.429937</v>
+      </c>
+      <c r="F16">
+        <v>146.738035</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A74628</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C11080</t>
-        </is>
-      </c>
-      <c r="I16">
-        <v>0.0002533333333333333</v>
+          <t>A78786</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>C12161</t>
+        </is>
       </c>
       <c r="J16">
-        <v>0.009155555555555556</v>
+        <v>0.0004098360655737705</v>
       </c>
       <c r="K16">
-        <v>22.84444444444444</v>
+        <v>0.00459016393442623</v>
       </c>
       <c r="L16">
-        <v>3.008888888888889</v>
+        <v>2.459016393442623</v>
       </c>
       <c r="M16">
-        <v>0.0004373333333333334</v>
+        <v>0.5409836065573771</v>
       </c>
       <c r="N16">
-        <v>2.222222222222222E-05</v>
+        <v>0.0001967213114754098</v>
       </c>
       <c r="O16">
-        <v>9.777777777777779E-06</v>
+        <v>8.19672131147541E-05</v>
       </c>
       <c r="P16">
-        <v>6.577777777777777E-05</v>
+        <v>8.19672131147541E-05</v>
       </c>
       <c r="Q16">
-        <v>0.01671111111111111</v>
+        <v>8.19672131147541E-05</v>
       </c>
       <c r="R16">
-        <v>0.0004488888888888889</v>
+        <v>0.0130327868852459</v>
       </c>
       <c r="S16">
-        <v>0.0005511111111111112</v>
+        <v>0.007967213114754099</v>
+      </c>
+      <c r="T16">
+        <v>4.098360655737705E-06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Haught-ReedBeds</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>-19.499366</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TSV-StuartCk</t>
+        </is>
       </c>
       <c r="E17">
-        <v>147.05127</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.321821</v>
+      </c>
+      <c r="F17">
+        <v>146.837451</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A74824</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C11102</t>
-        </is>
-      </c>
-      <c r="I17">
-        <v>0.0001412429378531073</v>
+          <t>A77316</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>C12142</t>
+        </is>
       </c>
       <c r="J17">
-        <v>0.001864406779661017</v>
+        <v>0.0002427184466019417</v>
       </c>
       <c r="K17">
-        <v>2.542372881355932</v>
+        <v>0.002330097087378641</v>
       </c>
       <c r="L17">
-        <v>0.5480225988700564</v>
+        <v>0.9708737864077669</v>
       </c>
       <c r="M17">
-        <v>0.006610169491525424</v>
+        <v>0.3592233009708738</v>
       </c>
       <c r="N17">
-        <v>2.824858757062147E-05</v>
+        <v>0.001718446601941748</v>
       </c>
       <c r="O17">
-        <v>5.649717514124294E-06</v>
+        <v>4.854368932038835E-05</v>
       </c>
       <c r="P17">
-        <v>7.909604519774011E-05</v>
+        <v>0.0001941747572815534</v>
       </c>
       <c r="Q17">
-        <v>0.00903954802259887</v>
+        <v>0.0001553398058252427</v>
       </c>
       <c r="R17">
-        <v>0.002858757062146893</v>
+        <v>0.007407766990291262</v>
       </c>
       <c r="S17">
-        <v>1.412429378531073E-06</v>
+        <v>0.002456310679611651</v>
+      </c>
+      <c r="T17">
+        <v>5.825242718446601E-06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ross-mouth</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>-19.275335</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ross-dam</t>
+        </is>
       </c>
       <c r="E18">
-        <v>146.830675</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.429937</v>
+      </c>
+      <c r="F18">
+        <v>146.738035</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A74699</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C11106</t>
-        </is>
-      </c>
-      <c r="I18">
-        <v>3.586800573888092E-05</v>
+          <t>A83992</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C11227</t>
+        </is>
       </c>
       <c r="J18">
-        <v>0.009449152542372882</v>
+        <v>0.000423728813559322</v>
       </c>
       <c r="K18">
-        <v>23.51694915254237</v>
+        <v>0.005254237288135594</v>
       </c>
       <c r="L18">
-        <v>3.199152542372881</v>
+        <v>2.372881355932203</v>
       </c>
       <c r="M18">
-        <v>1.016949152542373E-05</v>
+        <v>0.4915254237288135</v>
       </c>
       <c r="N18">
-        <v>1.059322033898305E-05</v>
+        <v>0.001779661016949152</v>
       </c>
       <c r="O18">
-        <v>1.059322033898305E-06</v>
+        <v>8.474576271186441E-05</v>
       </c>
       <c r="P18">
-        <v>4.661016949152542E-06</v>
+        <v>5.084745762711864E-05</v>
       </c>
       <c r="Q18">
-        <v>0.002830188679245283</v>
+        <v>0.0001694915254237288</v>
       </c>
       <c r="R18">
-        <v>1.652542372881356E-05</v>
+        <v>0.0106271186440678</v>
       </c>
       <c r="S18">
-        <v>2.288135593220339E-06</v>
+        <v>0.003288135593220339</v>
+      </c>
+      <c r="T18">
+        <v>4.23728813559322E-06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1635,274 +1725,294 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ingham-CattleCk</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>-18.714525</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Burd-AboveDam</t>
+        </is>
       </c>
       <c r="E19">
-        <v>146.108619</v>
-      </c>
-      <c r="F19" t="inlineStr">
+        <v>-21.08472</v>
+      </c>
+      <c r="F19">
+        <v>146.87056</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>A74837</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C11108</t>
-        </is>
-      </c>
-      <c r="I19">
-        <v>0.001</v>
+          <t>QH</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C11131</t>
+        </is>
       </c>
       <c r="J19">
-        <v>0.006</v>
+        <v>0.0002906976744186046</v>
       </c>
       <c r="K19">
-        <v>5.2</v>
+        <v>0.004651162790697674</v>
       </c>
       <c r="L19">
-        <v>0.6</v>
+        <v>1.511627906976744</v>
       </c>
       <c r="M19">
-        <v>0.01304</v>
+        <v>0.6860465116279071</v>
       </c>
       <c r="N19">
-        <v>0.0002</v>
+        <v>0.0001279069767441861</v>
       </c>
       <c r="O19">
-        <v>0.00024</v>
+        <v>5.813953488372093E-05</v>
       </c>
       <c r="P19">
-        <v>0.0005200000000000001</v>
+        <v>0.0001046511627906977</v>
       </c>
       <c r="Q19">
-        <v>0.00776</v>
+        <v>0.000372093023255814</v>
       </c>
       <c r="R19">
-        <v>0.006959999999999999</v>
+        <v>0.0122093023255814</v>
       </c>
       <c r="S19">
-        <v>0.00012</v>
+        <v>0.005244186046511628</v>
+      </c>
+      <c r="T19">
+        <v>1.27906976744186E-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ross-Aplins</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>-19.30468</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Haught-ReedBeds</t>
+        </is>
       </c>
       <c r="E20">
-        <v>146.781019</v>
-      </c>
-      <c r="F20" t="inlineStr">
+        <v>-19.499366</v>
+      </c>
+      <c r="F20">
+        <v>147.05127</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>A74629</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C11114</t>
-        </is>
-      </c>
-      <c r="I20">
-        <v>0.0003623188405797101</v>
+          <t>A83991</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C12173</t>
+        </is>
       </c>
       <c r="J20">
-        <v>0.002463768115942029</v>
+        <v>0.0002717391304347826</v>
       </c>
       <c r="K20">
-        <v>1.304347826086957</v>
+        <v>0.0025</v>
       </c>
       <c r="L20">
-        <v>0.391304347826087</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="M20">
-        <v>0.0004347826086956522</v>
+        <v>0.5108695652173914</v>
       </c>
       <c r="N20">
-        <v>7.246376811594203E-05</v>
+        <v>0.03695652173913044</v>
       </c>
       <c r="O20">
-        <v>0.0001449275362318841</v>
+        <v>0.0001195652173913044</v>
       </c>
       <c r="P20">
-        <v>0.001043478260869565</v>
+        <v>7.608695652173912E-05</v>
       </c>
       <c r="Q20">
-        <v>0.008869565217391304</v>
+        <v>0.0002282608695652174</v>
       </c>
       <c r="R20">
-        <v>0.004565217391304348</v>
+        <v>0.008793478260869566</v>
       </c>
       <c r="S20">
-        <v>3.623188405797101E-05</v>
+        <v>0.002706521739130435</v>
+      </c>
+      <c r="T20">
+        <v>2.717391304347826E-06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Burd-AboveDam</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>-19.81759</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TSV-Bluewater</t>
+        </is>
       </c>
       <c r="E21">
-        <v>146.09268</v>
-      </c>
-      <c r="F21" t="inlineStr">
+        <v>-19.176311</v>
+      </c>
+      <c r="F21">
+        <v>146.552749</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>QH</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C11119</t>
-        </is>
-      </c>
-      <c r="I21">
-        <v>0.00015625</v>
+          <t>A74823</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>C12174</t>
+        </is>
       </c>
       <c r="J21">
-        <v>0.001375</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="K21">
-        <v>2.5</v>
+        <v>0.01</v>
       </c>
       <c r="L21">
-        <v>1.1875</v>
+        <v>6.666666666666666</v>
       </c>
       <c r="M21">
-        <v>0.00035625</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N21">
-        <v>3.125E-05</v>
+        <v>0.005722222222222222</v>
       </c>
       <c r="O21">
-        <v>5E-05</v>
+        <v>0.0002777777777777778</v>
       </c>
       <c r="P21">
-        <v>3.125E-05</v>
+        <v>0.0001111111111111111</v>
       </c>
       <c r="Q21">
-        <v>0.003525</v>
+        <v>0.0002777777777777778</v>
       </c>
       <c r="R21">
-        <v>0.00128125</v>
+        <v>0.009722222222222222</v>
       </c>
       <c r="S21">
-        <v>1.5625E-06</v>
+        <v>0.002666666666666667</v>
+      </c>
+      <c r="T21">
+        <v>4.444444444444445E-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ross-Blacks</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>-19.34905</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Burd-Barrattas</t>
+        </is>
       </c>
       <c r="E22">
-        <v>146.73166</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.56949</v>
+      </c>
+      <c r="F22">
+        <v>147.222052</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A74701</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C11123</t>
-        </is>
-      </c>
-      <c r="I22">
-        <v>3.586800573888092E-05</v>
+          <t>A75501</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>C11027</t>
+        </is>
       </c>
       <c r="J22">
-        <v>0.002113821138211382</v>
+        <v>0.0002976190476190476</v>
       </c>
       <c r="K22">
-        <v>2.439024390243902</v>
+        <v>0.005</v>
       </c>
       <c r="L22">
-        <v>0.4471544715447154</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="M22">
-        <v>0.0002926829268292683</v>
+        <v>0.488095238095238</v>
       </c>
       <c r="N22">
-        <v>4.065040650406504E-05</v>
+        <v>0.0009285714285714286</v>
       </c>
       <c r="O22">
-        <v>2.439024390243902E-05</v>
+        <v>5.952380952380952E-05</v>
       </c>
       <c r="P22">
-        <v>0.0002439024390243902</v>
+        <v>0.0002380952380952381</v>
       </c>
       <c r="Q22">
-        <v>0.007626016260162602</v>
+        <v>0.004119047619047619</v>
       </c>
       <c r="R22">
-        <v>0.002804878048780488</v>
+        <v>0.01057142857142857</v>
       </c>
       <c r="S22">
-        <v>2.032520325203252E-06</v>
+        <v>0.005333333333333333</v>
+      </c>
+      <c r="T22">
+        <v>8.333333333333334E-06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1911,338 +2021,363 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AIMS-bridge</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>-19.395186</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ross-Aplins</t>
+        </is>
       </c>
       <c r="E23">
-        <v>147.022964</v>
-      </c>
-      <c r="F23" t="inlineStr">
+        <v>-19.30468</v>
+      </c>
+      <c r="F23">
+        <v>146.781019</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>A74633</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C11126</t>
-        </is>
-      </c>
-      <c r="I23">
-        <v>0.0001582278481012658</v>
+          <t>A83997</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C11777</t>
+        </is>
       </c>
       <c r="J23">
-        <v>0.007025316455696202</v>
+        <v>0.0002358490566037736</v>
       </c>
       <c r="K23">
-        <v>16.0126582278481</v>
+        <v>0.001320754716981132</v>
       </c>
       <c r="L23">
-        <v>1.936708860759494</v>
+        <v>2.075471698113208</v>
       </c>
       <c r="M23">
-        <v>0.00509493670886076</v>
+        <v>0.4622641509433963</v>
       </c>
       <c r="N23">
-        <v>3.164556962025317E-05</v>
+        <v>0.0007264150943396227</v>
       </c>
       <c r="O23">
-        <v>3.797468354430379E-05</v>
+        <v>4.716981132075471E-05</v>
       </c>
       <c r="P23">
-        <v>8.227848101265823E-05</v>
+        <v>5.660377358490566E-05</v>
       </c>
       <c r="Q23">
-        <v>0.01234177215189873</v>
+        <v>0.001207547169811321</v>
       </c>
       <c r="R23">
-        <v>0.000569620253164557</v>
+        <v>0.005226415094339623</v>
       </c>
       <c r="S23">
-        <v>0.0007721518987341771</v>
+        <v>0.0006603773584905661</v>
+      </c>
+      <c r="T23">
+        <v>2.358490566037736E-06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TSV-Bohle-fresh</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>-19.3201</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ross-Gleesons</t>
+        </is>
       </c>
       <c r="E24">
-        <v>146.70096</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.315906</v>
+      </c>
+      <c r="F24">
+        <v>146.736257</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>QH</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C11127</t>
-        </is>
-      </c>
-      <c r="I24">
-        <v>5.208333333333334E-05</v>
+          <t>A83989</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>C11058</t>
+        </is>
       </c>
       <c r="J24">
-        <v>0.0008333333333333334</v>
+        <v>0.0002336448598130841</v>
       </c>
       <c r="K24">
-        <v>4.375</v>
+        <v>0.002523364485981308</v>
       </c>
       <c r="L24">
-        <v>0.4166666666666667</v>
+        <v>2.05607476635514</v>
       </c>
       <c r="M24">
-        <v>0.00020625</v>
+        <v>0.4672897196261683</v>
       </c>
       <c r="N24">
-        <v>1.041666666666667E-05</v>
+        <v>0.0006542056074766356</v>
       </c>
       <c r="O24">
-        <v>8.333333333333334E-06</v>
+        <v>4.672897196261682E-05</v>
       </c>
       <c r="P24">
-        <v>4.791666666666666E-05</v>
+        <v>4.672897196261682E-05</v>
       </c>
       <c r="Q24">
-        <v>0.0105625</v>
+        <v>0.0001214953271028037</v>
       </c>
       <c r="R24">
-        <v>0.005770833333333334</v>
+        <v>0.008542056074766356</v>
       </c>
       <c r="S24">
-        <v>1.041666666666667E-06</v>
+        <v>0.004289719626168224</v>
+      </c>
+      <c r="T24">
+        <v>2.336448598130841E-06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Burd-AboveDam</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>-21.08472</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Burd-Lillismere</t>
+        </is>
       </c>
       <c r="E25">
-        <v>146.87056</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.518036</v>
+      </c>
+      <c r="F25">
+        <v>147.419893</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>QH</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C11131</t>
-        </is>
-      </c>
-      <c r="I25">
-        <v>0.0002906976744186046</v>
+          <t>A77324</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>C11779</t>
+        </is>
       </c>
       <c r="J25">
-        <v>0.004651162790697674</v>
+        <v>0.0002604166666666667</v>
       </c>
       <c r="K25">
-        <v>1.511627906976744</v>
+        <v>0.004270833333333333</v>
       </c>
       <c r="L25">
-        <v>0.6860465116279071</v>
+        <v>2.5</v>
       </c>
       <c r="M25">
-        <v>0.0001279069767441861</v>
+        <v>0.5729166666666667</v>
       </c>
       <c r="N25">
-        <v>5.813953488372093E-05</v>
+        <v>0.007114583333333333</v>
       </c>
       <c r="O25">
-        <v>0.0001046511627906977</v>
+        <v>0.0001041666666666667</v>
       </c>
       <c r="P25">
-        <v>0.000372093023255814</v>
+        <v>0.00015625</v>
       </c>
       <c r="Q25">
-        <v>0.0122093023255814</v>
+        <v>0.0007395833333333333</v>
       </c>
       <c r="R25">
-        <v>0.005244186046511628</v>
+        <v>0.008635416666666668</v>
       </c>
       <c r="S25">
-        <v>1.27906976744186E-05</v>
+        <v>0.00209375</v>
+      </c>
+      <c r="T25">
+        <v>2.604166666666667E-06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Burd-mouth</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>-19.663637</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Upstart-Mtink</t>
+        </is>
       </c>
       <c r="E26">
-        <v>147.527879</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.773321</v>
+      </c>
+      <c r="F26">
+        <v>147.515773</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A74689</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C11132</t>
-        </is>
-      </c>
-      <c r="I26">
-        <v>3.586800573888092E-05</v>
+          <t>A74619</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C11151</t>
+        </is>
       </c>
       <c r="J26">
-        <v>0.009291553133514987</v>
+        <v>0.0002</v>
       </c>
       <c r="K26">
-        <v>23.97820163487738</v>
+        <v>0.00216</v>
       </c>
       <c r="L26">
-        <v>3.160762942779292</v>
+        <v>1.52</v>
       </c>
       <c r="M26">
-        <v>2.452316076294278E-05</v>
+        <v>0.68</v>
       </c>
       <c r="N26">
-        <v>1.362397820163488E-05</v>
+        <v>0.03136</v>
       </c>
       <c r="O26">
-        <v>1.08991825613079E-06</v>
+        <v>9.6E-05</v>
       </c>
       <c r="P26">
-        <v>4.904632152588556E-06</v>
+        <v>2.4E-05</v>
       </c>
       <c r="Q26">
-        <v>0.002830188679245283</v>
+        <v>0.000176</v>
       </c>
       <c r="R26">
-        <v>0.0001839237057220708</v>
+        <v>0.01136</v>
       </c>
       <c r="S26">
-        <v>8.719346049046322E-07</v>
+        <v>0.002784</v>
+      </c>
+      <c r="T26">
+        <v>5.92E-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Burd-Barrattas</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>-19.567973</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Burd-irrig</t>
+        </is>
       </c>
       <c r="E27">
-        <v>147.207072</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.58904</v>
+      </c>
+      <c r="F27">
+        <v>147.397985</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A74358</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C11138</t>
-        </is>
-      </c>
-      <c r="I27">
-        <v>0.0001373626373626374</v>
+          <t>A78787</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>C12186</t>
+        </is>
       </c>
       <c r="J27">
-        <v>0.001428571428571429</v>
+        <v>0.0002192982456140351</v>
       </c>
       <c r="K27">
-        <v>1.703296703296703</v>
+        <v>0.003245614035087719</v>
       </c>
       <c r="L27">
-        <v>0.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="M27">
-        <v>0.01192307692307692</v>
+        <v>0.6929824561403509</v>
       </c>
       <c r="N27">
-        <v>2.747252747252747E-05</v>
+        <v>0.0002017543859649123</v>
       </c>
       <c r="O27">
-        <v>4.945054945054945E-05</v>
+        <v>4.385964912280701E-05</v>
       </c>
       <c r="P27">
-        <v>0.0007582417582417583</v>
+        <v>7.894736842105263E-05</v>
       </c>
       <c r="Q27">
-        <v>0.01</v>
+        <v>4.385964912280701E-05</v>
       </c>
       <c r="R27">
-        <v>0.004181318681318681</v>
+        <v>0.01228070175438596</v>
       </c>
       <c r="S27">
-        <v>4.395604395604396E-05</v>
+        <v>0.003657894736842106</v>
+      </c>
+      <c r="T27">
+        <v>2.192982456140351E-06</v>
       </c>
     </row>
     <row r="28">
@@ -2251,136 +2386,146 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Upstart-CapeCk</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>-19.902055</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ross-Blacks</t>
+        </is>
       </c>
       <c r="E28">
-        <v>147.75906</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.34905</v>
+      </c>
+      <c r="F28">
+        <v>146.73166</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A77321</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C11142</t>
-        </is>
-      </c>
-      <c r="I28">
-        <v>0.0004545454545454545</v>
+          <t>A78526</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C12065</t>
+        </is>
       </c>
       <c r="J28">
-        <v>0.007272727272727273</v>
+        <v>0.0002475247524752475</v>
       </c>
       <c r="K28">
-        <v>1.272727272727273</v>
+        <v>0.00297029702970297</v>
       </c>
       <c r="L28">
-        <v>0.4363636363636363</v>
+        <v>2.673267326732673</v>
       </c>
       <c r="M28">
-        <v>0.002436363636363636</v>
+        <v>0.6039603960396039</v>
       </c>
       <c r="N28">
-        <v>9.09090909090909E-05</v>
+        <v>0.0002079207920792079</v>
       </c>
       <c r="O28">
-        <v>0.0003272727272727273</v>
+        <v>4.950495049504951E-05</v>
       </c>
       <c r="P28">
-        <v>0.0005454545454545455</v>
+        <v>9.900990099009901E-06</v>
       </c>
       <c r="Q28">
-        <v>0.01265454545454545</v>
+        <v>4.950495049504951E-05</v>
       </c>
       <c r="R28">
-        <v>0.008</v>
+        <v>0.01178217821782178</v>
       </c>
       <c r="S28">
-        <v>2.727272727272727E-05</v>
+        <v>0.00498019801980198</v>
+      </c>
+      <c r="T28">
+        <v>2.475247524752475E-06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Haught-ReidRiver</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>-19.75909</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Upstart-Mtink</t>
+        </is>
       </c>
       <c r="E29">
-        <v>146.83281</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.773321</v>
+      </c>
+      <c r="F29">
+        <v>147.515773</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>QH</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C11144</t>
-        </is>
-      </c>
-      <c r="I29">
-        <v>0.0001041666666666667</v>
+          <t>A74831</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>C11738</t>
+        </is>
       </c>
       <c r="J29">
-        <v>0.001208333333333333</v>
+        <v>0.0002293577981651376</v>
       </c>
       <c r="K29">
-        <v>1.25</v>
+        <v>0.002844036697247706</v>
       </c>
       <c r="L29">
-        <v>0.3666666666666667</v>
+        <v>2.110091743119266</v>
       </c>
       <c r="M29">
-        <v>0.01083333333333333</v>
+        <v>0.6788990825688074</v>
       </c>
       <c r="N29">
-        <v>2.083333333333333E-05</v>
+        <v>0.005073394495412844</v>
       </c>
       <c r="O29">
-        <v>2.5E-05</v>
+        <v>0.0001376146788990826</v>
       </c>
       <c r="P29">
-        <v>0.0005666666666666666</v>
+        <v>0.0001009174311926606</v>
       </c>
       <c r="Q29">
-        <v>0.006833333333333334</v>
+        <v>0.001155963302752294</v>
       </c>
       <c r="R29">
-        <v>0.001708333333333333</v>
+        <v>0.0118348623853211</v>
       </c>
       <c r="S29">
-        <v>1.375E-05</v>
+        <v>0.00344954128440367</v>
+      </c>
+      <c r="T29">
+        <v>2.293577981651376E-06</v>
       </c>
     </row>
     <row r="30">
@@ -2389,273 +2534,293 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Upstart-Mtink</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>-19.773321</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Haught-Giru</t>
+        </is>
       </c>
       <c r="E30">
-        <v>147.515773</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.512679</v>
+      </c>
+      <c r="F30">
+        <v>147.112332</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A74619</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C11151</t>
-        </is>
-      </c>
-      <c r="I30">
-        <v>0.0002</v>
+          <t>A74839</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C12166</t>
+        </is>
       </c>
       <c r="J30">
-        <v>0.00216</v>
+        <v>0.0001908396946564885</v>
       </c>
       <c r="K30">
-        <v>1.52</v>
+        <v>0.001679389312977099</v>
       </c>
       <c r="L30">
-        <v>0.68</v>
+        <v>1.984732824427481</v>
       </c>
       <c r="M30">
-        <v>0.03136</v>
+        <v>0.5114503816793894</v>
       </c>
       <c r="N30">
-        <v>9.6E-05</v>
+        <v>0.0001297709923664122</v>
       </c>
       <c r="O30">
-        <v>2.4E-05</v>
+        <v>3.816793893129771E-05</v>
       </c>
       <c r="P30">
-        <v>0.000176</v>
+        <v>3.053435114503817E-05</v>
       </c>
       <c r="Q30">
-        <v>0.01136</v>
+        <v>3.816793893129771E-05</v>
       </c>
       <c r="R30">
-        <v>0.002784</v>
+        <v>0.009618320610687023</v>
       </c>
       <c r="S30">
-        <v>5.92E-05</v>
+        <v>0.00333587786259542</v>
+      </c>
+      <c r="T30">
+        <v>1.908396946564886E-06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Burd-AboveDam</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>-20.99895</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Burd-mouth</t>
+        </is>
       </c>
       <c r="E31">
-        <v>146.42632</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.663637</v>
+      </c>
+      <c r="F31">
+        <v>147.527879</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>QH</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C11161</t>
-        </is>
-      </c>
-      <c r="I31">
-        <v>8.620689655172413E-05</v>
+          <t>A83994</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C11751</t>
+        </is>
       </c>
       <c r="J31">
-        <v>0.001413793103448276</v>
+        <v>0.0003125</v>
       </c>
       <c r="K31">
-        <v>0.6896551724137931</v>
+        <v>0.00575</v>
       </c>
       <c r="L31">
-        <v>0.4137931034482759</v>
+        <v>4.375</v>
       </c>
       <c r="M31">
-        <v>0.004551724137931035</v>
+        <v>0.6875</v>
       </c>
       <c r="N31">
-        <v>4.137931034482759E-05</v>
+        <v>0.0004875</v>
       </c>
       <c r="O31">
-        <v>2.758620689655173E-05</v>
+        <v>6.25E-05</v>
       </c>
       <c r="P31">
-        <v>1.724137931034483E-05</v>
+        <v>0.000225</v>
       </c>
       <c r="Q31">
-        <v>0.01003448275862069</v>
+        <v>0.00365</v>
       </c>
       <c r="R31">
-        <v>0.003448275862068965</v>
+        <v>0.0108375</v>
       </c>
       <c r="S31">
-        <v>8.620689655172415E-07</v>
+        <v>0.0034875</v>
+      </c>
+      <c r="T31">
+        <v>3.125E-06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Haught-Giru</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>-19.512679</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Guth-SaltCk</t>
+        </is>
       </c>
       <c r="E32">
-        <v>147.112332</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.948344</v>
+      </c>
+      <c r="F32">
+        <v>147.922379</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A74700</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C11167</t>
-        </is>
-      </c>
-      <c r="I32">
-        <v>3.586800573888092E-05</v>
+          <t>A83993</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>C11182</t>
+        </is>
       </c>
       <c r="J32">
-        <v>0.002846153846153846</v>
+        <v>0.0002032520325203252</v>
       </c>
       <c r="K32">
-        <v>2.846153846153846</v>
+        <v>0.003170731707317073</v>
       </c>
       <c r="L32">
-        <v>0.7923076923076924</v>
+        <v>2.113821138211382</v>
       </c>
       <c r="M32">
-        <v>0.0001384615384615385</v>
+        <v>0.5609756097560975</v>
       </c>
       <c r="N32">
-        <v>3.846153846153846E-05</v>
+        <v>0.003731707317073171</v>
       </c>
       <c r="O32">
-        <v>4.615384615384615E-05</v>
+        <v>4.065040650406504E-05</v>
       </c>
       <c r="P32">
-        <v>0.0003384615384615385</v>
+        <v>8.943089430894309E-05</v>
       </c>
       <c r="Q32">
-        <v>0.01053846153846154</v>
+        <v>9.756097560975609E-05</v>
       </c>
       <c r="R32">
-        <v>0.002476923076923077</v>
+        <v>0.008292682926829269</v>
       </c>
       <c r="S32">
-        <v>1.538461538461538E-05</v>
+        <v>0.006211382113821139</v>
+      </c>
+      <c r="T32">
+        <v>2.032520325203252E-06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Guth-SaltCk</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>-19.948344</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Burd-Lillismere</t>
+        </is>
       </c>
       <c r="E33">
-        <v>147.922379</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.518036</v>
+      </c>
+      <c r="F33">
+        <v>147.419893</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A83993</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C11182</t>
-        </is>
-      </c>
-      <c r="I33">
+          <t>A74832</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C12194</t>
+        </is>
+      </c>
+      <c r="J33">
         <v>0.0002032520325203252</v>
       </c>
-      <c r="J33">
-        <v>0.003170731707317073</v>
-      </c>
       <c r="K33">
+        <v>0.002195121951219512</v>
+      </c>
+      <c r="L33">
         <v>2.113821138211382</v>
       </c>
-      <c r="L33">
-        <v>0.5609756097560975</v>
-      </c>
       <c r="M33">
-        <v>0.003731707317073171</v>
+        <v>0.6910569105691057</v>
       </c>
       <c r="N33">
+        <v>7.317073170731707E-05</v>
+      </c>
+      <c r="O33">
         <v>4.065040650406504E-05</v>
       </c>
-      <c r="O33">
-        <v>8.943089430894309E-05</v>
-      </c>
       <c r="P33">
-        <v>9.756097560975609E-05</v>
+        <v>4.065040650406504E-05</v>
       </c>
       <c r="Q33">
-        <v>0.008292682926829269</v>
+        <v>4.065040650406504E-05</v>
       </c>
       <c r="R33">
-        <v>0.006211382113821139</v>
+        <v>0.007195121951219513</v>
       </c>
       <c r="S33">
+        <v>0.002170731707317073</v>
+      </c>
+      <c r="T33">
         <v>2.032520325203252E-06</v>
       </c>
     </row>
@@ -2670,62 +2835,67 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ross-dam</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>-19.429937</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Haught-Crooked</t>
+        </is>
       </c>
       <c r="E34">
-        <v>146.738035</v>
-      </c>
-      <c r="F34" t="inlineStr">
+        <v>-19.517805</v>
+      </c>
+      <c r="F34">
+        <v>147.093768</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>A83992</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C11227</t>
-        </is>
-      </c>
-      <c r="I34">
-        <v>0.000423728813559322</v>
+          <t>A74830</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C11765</t>
+        </is>
       </c>
       <c r="J34">
-        <v>0.005254237288135594</v>
+        <v>0.0001953125</v>
       </c>
       <c r="K34">
-        <v>2.372881355932203</v>
+        <v>0.003125</v>
       </c>
       <c r="L34">
-        <v>0.4915254237288135</v>
+        <v>2.65625</v>
       </c>
       <c r="M34">
-        <v>0.001779661016949152</v>
+        <v>0.4296875</v>
       </c>
       <c r="N34">
-        <v>8.474576271186441E-05</v>
+        <v>0.0043203125</v>
       </c>
       <c r="O34">
-        <v>5.084745762711864E-05</v>
+        <v>3.90625E-05</v>
       </c>
       <c r="P34">
-        <v>0.0001694915254237288</v>
+        <v>6.25E-05</v>
       </c>
       <c r="Q34">
-        <v>0.0106271186440678</v>
+        <v>0.0004375</v>
       </c>
       <c r="R34">
-        <v>0.003288135593220339</v>
+        <v>0.0071796875</v>
       </c>
       <c r="S34">
-        <v>4.23728813559322E-06</v>
+        <v>0.001984375</v>
+      </c>
+      <c r="T34">
+        <v>1.953125E-06</v>
       </c>
     </row>
     <row r="35">
@@ -2734,67 +2904,72 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Burd-JeronaRd</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>-19.513845</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Haught-Giru</t>
+        </is>
       </c>
       <c r="E35">
-        <v>147.218784</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.512679</v>
+      </c>
+      <c r="F35">
+        <v>147.112332</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A83988</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C11732</t>
-        </is>
-      </c>
-      <c r="I35">
-        <v>0.0003164556962025317</v>
+          <t>A75601</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>C12085</t>
+        </is>
       </c>
       <c r="J35">
-        <v>0.006835443037974683</v>
+        <v>0.0001908396946564885</v>
       </c>
       <c r="K35">
-        <v>4.810126582278481</v>
+        <v>0.002977099236641221</v>
       </c>
       <c r="L35">
-        <v>0.670886075949367</v>
+        <v>1.984732824427481</v>
       </c>
       <c r="M35">
-        <v>0.004974683544303797</v>
+        <v>0.7022900763358778</v>
       </c>
       <c r="N35">
-        <v>6.329113924050633E-05</v>
+        <v>0.0009236641221374045</v>
       </c>
       <c r="O35">
-        <v>0.0002025316455696203</v>
+        <v>3.816793893129771E-05</v>
       </c>
       <c r="P35">
-        <v>0.001075949367088608</v>
+        <v>3.816793893129771E-05</v>
       </c>
       <c r="Q35">
-        <v>0.01043037974683544</v>
+        <v>3.816793893129771E-05</v>
       </c>
       <c r="R35">
-        <v>0.004012658227848101</v>
+        <v>0.01229007633587786</v>
       </c>
       <c r="S35">
-        <v>1.645569620253165E-05</v>
+        <v>0.003458015267175573</v>
+      </c>
+      <c r="T35">
+        <v>1.908396946564886E-06</v>
       </c>
     </row>
     <row r="36">
@@ -2808,683 +2983,733 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Upstart-Mtink</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>-19.773321</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Burd-JeronaRd</t>
+        </is>
       </c>
       <c r="E36">
-        <v>147.515773</v>
-      </c>
-      <c r="F36" t="inlineStr">
+        <v>-19.513845</v>
+      </c>
+      <c r="F36">
+        <v>147.218784</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>A74831</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C11738</t>
-        </is>
-      </c>
-      <c r="I36">
-        <v>0.0002293577981651376</v>
+          <t>A83988</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>C11732</t>
+        </is>
       </c>
       <c r="J36">
-        <v>0.002844036697247706</v>
+        <v>0.0003164556962025317</v>
       </c>
       <c r="K36">
-        <v>2.110091743119266</v>
+        <v>0.006835443037974683</v>
       </c>
       <c r="L36">
-        <v>0.6788990825688074</v>
+        <v>4.810126582278481</v>
       </c>
       <c r="M36">
-        <v>0.005073394495412844</v>
+        <v>0.670886075949367</v>
       </c>
       <c r="N36">
-        <v>0.0001376146788990826</v>
+        <v>0.004974683544303797</v>
       </c>
       <c r="O36">
-        <v>0.0001009174311926606</v>
+        <v>6.329113924050633E-05</v>
       </c>
       <c r="P36">
-        <v>0.001155963302752294</v>
+        <v>0.0002025316455696203</v>
       </c>
       <c r="Q36">
-        <v>0.0118348623853211</v>
+        <v>0.001075949367088608</v>
       </c>
       <c r="R36">
-        <v>0.00344954128440367</v>
+        <v>0.01043037974683544</v>
       </c>
       <c r="S36">
-        <v>2.293577981651376E-06</v>
+        <v>0.004012658227848101</v>
+      </c>
+      <c r="T36">
+        <v>1.645569620253165E-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Haught-Giru</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>-19.512679</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Burd-AboveDam</t>
+        </is>
       </c>
       <c r="E37">
-        <v>147.112332</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-20.99895</v>
+      </c>
+      <c r="F37">
+        <v>146.42632</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>A83986</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C11745</t>
-        </is>
-      </c>
-      <c r="I37">
-        <v>0.0004464285714285714</v>
+          <t>QH</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C11161</t>
+        </is>
       </c>
       <c r="J37">
-        <v>0.004464285714285714</v>
+        <v>8.620689655172413E-05</v>
       </c>
       <c r="K37">
-        <v>1.785714285714286</v>
+        <v>0.001413793103448276</v>
       </c>
       <c r="L37">
-        <v>0.4464285714285715</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="M37">
-        <v>0.001696428571428571</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="N37">
-        <v>8.928571428571429E-05</v>
+        <v>0.004551724137931035</v>
       </c>
       <c r="O37">
-        <v>0.0002321428571428571</v>
+        <v>4.137931034482759E-05</v>
       </c>
       <c r="P37">
-        <v>0.003392857142857143</v>
+        <v>2.758620689655173E-05</v>
       </c>
       <c r="Q37">
-        <v>0.009232142857142857</v>
+        <v>1.724137931034483E-05</v>
       </c>
       <c r="R37">
-        <v>0.004928571428571429</v>
+        <v>0.01003448275862069</v>
       </c>
       <c r="S37">
-        <v>1.071428571428571E-05</v>
+        <v>0.003448275862068965</v>
+      </c>
+      <c r="T37">
+        <v>8.620689655172415E-07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Burd-mouth</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>-19.663637</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Upstart-Mtink</t>
+        </is>
       </c>
       <c r="E38">
-        <v>147.527879</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.773321</v>
+      </c>
+      <c r="F38">
+        <v>147.515773</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A83994</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C11751</t>
-        </is>
-      </c>
-      <c r="I38">
-        <v>0.0003125</v>
+          <t>A74844</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>C12107</t>
+        </is>
       </c>
       <c r="J38">
-        <v>0.00575</v>
+        <v>0.00015527950310559</v>
       </c>
       <c r="K38">
-        <v>4.375</v>
+        <v>0.002298136645962733</v>
       </c>
       <c r="L38">
-        <v>0.6875</v>
+        <v>2.111801242236025</v>
       </c>
       <c r="M38">
-        <v>0.0004875</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="N38">
-        <v>6.25E-05</v>
+        <v>0.002670807453416149</v>
       </c>
       <c r="O38">
-        <v>0.000225</v>
+        <v>3.105590062111801E-05</v>
       </c>
       <c r="P38">
-        <v>0.00365</v>
+        <v>2.484472049689441E-05</v>
       </c>
       <c r="Q38">
-        <v>0.0108375</v>
+        <v>8.695652173913041E-05</v>
       </c>
       <c r="R38">
-        <v>0.0034875</v>
+        <v>0.0131055900621118</v>
       </c>
       <c r="S38">
-        <v>3.125E-06</v>
+        <v>0.003465838509316769</v>
+      </c>
+      <c r="T38">
+        <v>1.552795031055901E-06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Haught-Crooked</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>-19.517805</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Haught-ReidRiver</t>
+        </is>
       </c>
       <c r="E39">
-        <v>147.093768</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.75909</v>
+      </c>
+      <c r="F39">
+        <v>146.83281</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>A74830</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C11765</t>
-        </is>
-      </c>
-      <c r="I39">
-        <v>0.0001953125</v>
+          <t>QH</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>C11144</t>
+        </is>
       </c>
       <c r="J39">
-        <v>0.003125</v>
+        <v>0.0001041666666666667</v>
       </c>
       <c r="K39">
-        <v>2.65625</v>
+        <v>0.001208333333333333</v>
       </c>
       <c r="L39">
-        <v>0.4296875</v>
+        <v>1.25</v>
       </c>
       <c r="M39">
-        <v>0.0043203125</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="N39">
-        <v>3.90625E-05</v>
+        <v>0.01083333333333333</v>
       </c>
       <c r="O39">
-        <v>6.25E-05</v>
+        <v>2.083333333333333E-05</v>
       </c>
       <c r="P39">
-        <v>0.0004375</v>
+        <v>2.5E-05</v>
       </c>
       <c r="Q39">
-        <v>0.0071796875</v>
+        <v>0.0005666666666666666</v>
       </c>
       <c r="R39">
-        <v>0.001984375</v>
+        <v>0.006833333333333334</v>
       </c>
       <c r="S39">
-        <v>1.953125E-06</v>
+        <v>0.001708333333333333</v>
+      </c>
+      <c r="T39">
+        <v>1.375E-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TSV-Bluewater</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>-19.176311</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Burd-Barrattas</t>
+        </is>
       </c>
       <c r="E40">
-        <v>146.552749</v>
-      </c>
-      <c r="F40" t="inlineStr">
+        <v>-19.567973</v>
+      </c>
+      <c r="F40">
+        <v>147.207072</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>A83996</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C11768</t>
-        </is>
-      </c>
-      <c r="I40">
-        <v>0.003125</v>
+          <t>A74358</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C11138</t>
+        </is>
       </c>
       <c r="J40">
-        <v>0.01125</v>
+        <v>0.0001373626373626374</v>
       </c>
       <c r="K40">
-        <v>7.5</v>
+        <v>0.001428571428571429</v>
       </c>
       <c r="L40">
-        <v>0.3125</v>
+        <v>1.703296703296703</v>
       </c>
       <c r="M40">
-        <v>0.006875</v>
+        <v>0.5</v>
       </c>
       <c r="N40">
-        <v>0.000625</v>
+        <v>0.01192307692307692</v>
       </c>
       <c r="O40">
-        <v>0.00025</v>
+        <v>2.747252747252747E-05</v>
       </c>
       <c r="P40">
-        <v>0.013</v>
+        <v>4.945054945054945E-05</v>
       </c>
       <c r="Q40">
-        <v>0.004225</v>
+        <v>0.0007582417582417583</v>
       </c>
       <c r="R40">
-        <v>0.002875</v>
+        <v>0.01</v>
       </c>
       <c r="S40">
-        <v>0.0001125</v>
+        <v>0.004181318681318681</v>
+      </c>
+      <c r="T40">
+        <v>4.395604395604396E-05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ross-Aplins</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>-19.30468</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Haught-ReedBeds</t>
+        </is>
       </c>
       <c r="E41">
-        <v>146.781019</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.499366</v>
+      </c>
+      <c r="F41">
+        <v>147.05127</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A83997</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C11777</t>
-        </is>
-      </c>
-      <c r="I41">
-        <v>0.0002358490566037736</v>
+          <t>A74824</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C11102</t>
+        </is>
       </c>
       <c r="J41">
-        <v>0.001320754716981132</v>
+        <v>0.0001412429378531073</v>
       </c>
       <c r="K41">
-        <v>2.075471698113208</v>
+        <v>0.001864406779661017</v>
       </c>
       <c r="L41">
-        <v>0.4622641509433963</v>
+        <v>2.542372881355932</v>
       </c>
       <c r="M41">
-        <v>0.0007264150943396227</v>
+        <v>0.5480225988700564</v>
       </c>
       <c r="N41">
-        <v>4.716981132075471E-05</v>
+        <v>0.006610169491525424</v>
       </c>
       <c r="O41">
-        <v>5.660377358490566E-05</v>
+        <v>2.824858757062147E-05</v>
       </c>
       <c r="P41">
-        <v>0.001207547169811321</v>
+        <v>5.649717514124294E-06</v>
       </c>
       <c r="Q41">
-        <v>0.005226415094339623</v>
+        <v>7.909604519774011E-05</v>
       </c>
       <c r="R41">
-        <v>0.0006603773584905661</v>
+        <v>0.00903954802259887</v>
       </c>
       <c r="S41">
-        <v>2.358490566037736E-06</v>
+        <v>0.002858757062146893</v>
+      </c>
+      <c r="T41">
+        <v>1.412429378531073E-06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Burd-Lillismere</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>-19.518036</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Burd-Didge</t>
+        </is>
       </c>
       <c r="E42">
-        <v>147.419893</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.560723</v>
+      </c>
+      <c r="F42">
+        <v>147.247639</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A77324</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C11779</t>
-        </is>
-      </c>
-      <c r="I42">
-        <v>0.0002604166666666667</v>
+          <t>A74843</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C12081</t>
+        </is>
       </c>
       <c r="J42">
-        <v>0.004270833333333333</v>
+        <v>0.0001288659793814433</v>
       </c>
       <c r="K42">
-        <v>2.5</v>
+        <v>0.001494845360824742</v>
       </c>
       <c r="L42">
-        <v>0.5729166666666667</v>
+        <v>2.11340206185567</v>
       </c>
       <c r="M42">
-        <v>0.007114583333333333</v>
+        <v>0.5567010309278352</v>
       </c>
       <c r="N42">
-        <v>0.0001041666666666667</v>
+        <v>6.185567010309278E-05</v>
       </c>
       <c r="O42">
-        <v>0.00015625</v>
+        <v>2.577319587628866E-05</v>
       </c>
       <c r="P42">
-        <v>0.0007395833333333333</v>
+        <v>4.639175257731959E-05</v>
       </c>
       <c r="Q42">
-        <v>0.008635416666666668</v>
+        <v>2.577319587628866E-05</v>
       </c>
       <c r="R42">
-        <v>0.00209375</v>
+        <v>0.01025773195876289</v>
       </c>
       <c r="S42">
-        <v>2.604166666666667E-06</v>
+        <v>0.003201030927835052</v>
+      </c>
+      <c r="T42">
+        <v>1.288659793814433E-06</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ross-mouth</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>-19.275335</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Burd-AboveDam</t>
+        </is>
       </c>
       <c r="E43">
-        <v>146.830675</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.81759</v>
+      </c>
+      <c r="F43">
+        <v>146.09268</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A83990</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C11782</t>
-        </is>
-      </c>
-      <c r="I43">
-        <v>0.0002452830188679245</v>
+          <t>QH</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C11119</t>
+        </is>
       </c>
       <c r="J43">
-        <v>0.007877358490566038</v>
+        <v>0.00015625</v>
       </c>
       <c r="K43">
-        <v>25.18867924528302</v>
+        <v>0.001375</v>
       </c>
       <c r="L43">
-        <v>2.94811320754717</v>
+        <v>2.5</v>
       </c>
       <c r="M43">
-        <v>0.0008679245283018868</v>
+        <v>1.1875</v>
       </c>
       <c r="N43">
-        <v>2.358490566037736E-06</v>
+        <v>0.00035625</v>
       </c>
       <c r="O43">
-        <v>5.188679245283019E-06</v>
+        <v>3.125E-05</v>
       </c>
       <c r="P43">
-        <v>0.0001080188679245283</v>
+        <v>5E-05</v>
       </c>
       <c r="Q43">
-        <v>0.01820754716981132</v>
+        <v>3.125E-05</v>
       </c>
       <c r="R43">
-        <v>0.0001273584905660377</v>
+        <v>0.003525</v>
       </c>
       <c r="S43">
-        <v>5.188679245283019E-07</v>
+        <v>0.00128125</v>
+      </c>
+      <c r="T43">
+        <v>1.5625E-06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AIMS-bridge</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>-19.395186</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TSV-Bohle-fresh</t>
+        </is>
       </c>
       <c r="E44">
-        <v>147.022964</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.262559</v>
+      </c>
+      <c r="F44">
+        <v>146.705397</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>A77325</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C11790</t>
-        </is>
-      </c>
-      <c r="I44">
-        <v>0.0002377622377622378</v>
+          <t>A74366</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C12035</t>
+        </is>
       </c>
       <c r="J44">
-        <v>0.006321678321678322</v>
+        <v>0.0001572327044025157</v>
       </c>
       <c r="K44">
-        <v>17.34265734265734</v>
+        <v>0.002452830188679245</v>
       </c>
       <c r="L44">
-        <v>2.027972027972028</v>
+        <v>3.647798742138365</v>
       </c>
       <c r="M44">
-        <v>0.001342657342657343</v>
+        <v>0.220125786163522</v>
       </c>
       <c r="N44">
-        <v>1.398601398601399E-05</v>
+        <v>0.003308176100628931</v>
       </c>
       <c r="O44">
-        <v>1.258741258741259E-05</v>
+        <v>3.144654088050314E-05</v>
       </c>
       <c r="P44">
-        <v>3.216783216783217E-05</v>
+        <v>6.289308176100629E-05</v>
       </c>
       <c r="Q44">
-        <v>0.01440559440559441</v>
+        <v>0.0004654088050314466</v>
       </c>
       <c r="R44">
-        <v>0.0002671328671328671</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S44">
-        <v>3.076923076923077E-06</v>
+        <v>0.0008427672955974843</v>
+      </c>
+      <c r="T44">
+        <v>3.773584905660377E-06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cleveland-CrocCk</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>-19.387241</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ross-Aplins</t>
+        </is>
       </c>
       <c r="E45">
-        <v>147.014767</v>
-      </c>
-      <c r="F45" t="inlineStr">
+        <v>-19.30468</v>
+      </c>
+      <c r="F45">
+        <v>146.781019</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>A74826</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C12028</t>
-        </is>
-      </c>
-      <c r="I45">
-        <v>0.0002872727272727273</v>
+          <t>A78795</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C12105</t>
+        </is>
       </c>
       <c r="J45">
-        <v>0.005890909090909091</v>
+        <v>0.0002</v>
       </c>
       <c r="K45">
-        <v>24.72727272727273</v>
+        <v>0.00248</v>
       </c>
       <c r="L45">
-        <v>3.309090909090909</v>
+        <v>2.64</v>
       </c>
       <c r="M45">
-        <v>0.0006036363636363636</v>
+        <v>0.6559999999999998</v>
       </c>
       <c r="N45">
-        <v>9.090909090909091E-06</v>
+        <v>8.000000000000001E-05</v>
       </c>
       <c r="O45">
-        <v>1.818181818181818E-06</v>
+        <v>4E-05</v>
       </c>
       <c r="P45">
-        <v>9.090909090909091E-06</v>
+        <v>8E-06</v>
       </c>
       <c r="Q45">
-        <v>0.002830188679245283</v>
+        <v>4E-05</v>
       </c>
       <c r="R45">
-        <v>0.0001745454545454545</v>
+        <v>0.01152</v>
       </c>
       <c r="S45">
-        <v>1.963636363636364E-06</v>
+        <v>0.004192</v>
+      </c>
+      <c r="T45">
+        <v>2E-06</v>
       </c>
     </row>
     <row r="46">
@@ -3493,67 +3718,72 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TSV-Bohle</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>-19.25816</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Upstart-CapeCk</t>
+        </is>
       </c>
       <c r="E46">
-        <v>146.706871</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.902055</v>
+      </c>
+      <c r="F46">
+        <v>147.75906</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>A74841</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>C12029</t>
-        </is>
-      </c>
-      <c r="I46">
-        <v>0.000376425855513308</v>
+          <t>A74626</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>C11050</t>
+        </is>
       </c>
       <c r="J46">
-        <v>0.0004591104734576758</v>
+        <v>6.811989100817439E-05</v>
       </c>
       <c r="K46">
-        <v>24.44866920152091</v>
+        <v>0.001525885558583106</v>
       </c>
       <c r="L46">
-        <v>2.950570342205323</v>
+        <v>2.343324250681199</v>
       </c>
       <c r="M46">
-        <v>0.001159695817490494</v>
+        <v>0.4223433242506812</v>
       </c>
       <c r="N46">
-        <v>7.604562737642585E-06</v>
+        <v>0.00662125340599455</v>
       </c>
       <c r="O46">
-        <v>1.520912547528517E-06</v>
+        <v>2.724795640326975E-05</v>
       </c>
       <c r="P46">
-        <v>7.604562737642585E-06</v>
+        <v>1.907356948228883E-05</v>
       </c>
       <c r="Q46">
-        <v>0.002830188679245283</v>
+        <v>8.991825613079019E-05</v>
       </c>
       <c r="R46">
-        <v>0.0005703422053231939</v>
+        <v>0.01040871934604905</v>
       </c>
       <c r="S46">
-        <v>2.509505703422054E-06</v>
+        <v>0.004713896457765668</v>
+      </c>
+      <c r="T46">
+        <v>9.209809264305177E-05</v>
       </c>
     </row>
     <row r="47">
@@ -3562,72 +3792,77 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>August</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TSV-Bohle-fresh</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>-19.262559</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Haught-Crooked</t>
+        </is>
       </c>
       <c r="E47">
-        <v>146.705397</v>
-      </c>
-      <c r="F47" t="inlineStr">
+        <v>-19.517772</v>
+      </c>
+      <c r="F47">
+        <v>147.090193</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>A74366</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>C12035</t>
-        </is>
-      </c>
-      <c r="I47">
-        <v>0.0001572327044025157</v>
+          <t>A74838</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C12199</t>
+        </is>
       </c>
       <c r="J47">
-        <v>0.002452830188679245</v>
+        <v>9.025270758122743E-05</v>
       </c>
       <c r="K47">
-        <v>3.647798742138365</v>
+        <v>0.002779783393501805</v>
       </c>
       <c r="L47">
-        <v>0.220125786163522</v>
+        <v>5.270758122743683</v>
       </c>
       <c r="M47">
-        <v>0.003308176100628931</v>
+        <v>0.6714801444043322</v>
       </c>
       <c r="N47">
-        <v>3.144654088050314E-05</v>
+        <v>0.002379061371841156</v>
       </c>
       <c r="O47">
-        <v>6.289308176100629E-05</v>
+        <v>1.805054151624549E-05</v>
       </c>
       <c r="P47">
-        <v>0.0004654088050314466</v>
+        <v>2.166064981949458E-05</v>
       </c>
       <c r="Q47">
-        <v>0.002830188679245283</v>
+        <v>1.805054151624549E-05</v>
       </c>
       <c r="R47">
-        <v>0.0008427672955974843</v>
+        <v>0.008555956678700362</v>
       </c>
       <c r="S47">
-        <v>3.773584905660377E-06</v>
+        <v>0.001613718411552347</v>
+      </c>
+      <c r="T47">
+        <v>9.025270758122744E-07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3636,67 +3871,72 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ross-Blacks</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>-19.34905</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TSV-StuartCk</t>
+        </is>
       </c>
       <c r="E48">
-        <v>146.73166</v>
-      </c>
-      <c r="F48" t="inlineStr">
+        <v>-19.321821</v>
+      </c>
+      <c r="F48">
+        <v>146.837451</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>A78526</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C12065</t>
-        </is>
-      </c>
-      <c r="I48">
-        <v>0.0002475247524752475</v>
+          <t>A74820</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C12167</t>
+        </is>
       </c>
       <c r="J48">
-        <v>0.00297029702970297</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K48">
-        <v>2.673267326732673</v>
+        <v>0.0004591104734576758</v>
       </c>
       <c r="L48">
-        <v>0.6039603960396039</v>
+        <v>1.822094691535151</v>
       </c>
       <c r="M48">
-        <v>0.0002079207920792079</v>
+        <v>0.5796269727403156</v>
       </c>
       <c r="N48">
-        <v>4.950495049504951E-05</v>
+        <v>0.004433285509325682</v>
       </c>
       <c r="O48">
-        <v>9.900990099009901E-06</v>
+        <v>7.173601147776184E-06</v>
       </c>
       <c r="P48">
-        <v>4.950495049504951E-05</v>
+        <v>1.434720229555237E-06</v>
       </c>
       <c r="Q48">
-        <v>0.01178217821782178</v>
+        <v>7.173601147776184E-06</v>
       </c>
       <c r="R48">
-        <v>0.00498019801980198</v>
+        <v>0.005523672883787661</v>
       </c>
       <c r="S48">
-        <v>2.475247524752475E-06</v>
+        <v>0.001352941176470588</v>
+      </c>
+      <c r="T48">
+        <v>3.586800573888092E-07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3705,131 +3945,141 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Burd-Didge</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>-19.560723</v>
+          <t>fresh</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TSV-Bohle-fresh</t>
+        </is>
       </c>
       <c r="E49">
-        <v>147.247639</v>
-      </c>
-      <c r="F49" t="inlineStr">
+        <v>-19.3201</v>
+      </c>
+      <c r="F49">
+        <v>146.70096</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>A74843</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C12081</t>
-        </is>
-      </c>
-      <c r="I49">
-        <v>0.0001288659793814433</v>
+          <t>QH</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C11127</t>
+        </is>
       </c>
       <c r="J49">
-        <v>0.001494845360824742</v>
+        <v>5.208333333333334E-05</v>
       </c>
       <c r="K49">
-        <v>2.11340206185567</v>
+        <v>0.0008333333333333334</v>
       </c>
       <c r="L49">
-        <v>0.5567010309278352</v>
+        <v>4.375</v>
       </c>
       <c r="M49">
-        <v>6.185567010309278E-05</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N49">
-        <v>2.577319587628866E-05</v>
+        <v>0.00020625</v>
       </c>
       <c r="O49">
-        <v>4.639175257731959E-05</v>
+        <v>1.041666666666667E-05</v>
       </c>
       <c r="P49">
-        <v>2.577319587628866E-05</v>
+        <v>8.333333333333334E-06</v>
       </c>
       <c r="Q49">
-        <v>0.01025773195876289</v>
+        <v>4.791666666666666E-05</v>
       </c>
       <c r="R49">
-        <v>0.003201030927835052</v>
+        <v>0.0105625</v>
       </c>
       <c r="S49">
-        <v>1.288659793814433E-06</v>
+        <v>0.005770833333333334</v>
+      </c>
+      <c r="T49">
+        <v>1.041666666666667E-06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Haught-Giru</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>-19.512679</v>
+          <t>brackish</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AIMS-bridge</t>
+        </is>
       </c>
       <c r="E50">
-        <v>147.112332</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.395186</v>
+      </c>
+      <c r="F50">
+        <v>147.022964</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A75601</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C12085</t>
-        </is>
-      </c>
-      <c r="I50">
-        <v>0.0001908396946564885</v>
+          <t>A74633</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>C11126</t>
+        </is>
       </c>
       <c r="J50">
-        <v>0.002977099236641221</v>
+        <v>0.0001582278481012658</v>
       </c>
       <c r="K50">
-        <v>1.984732824427481</v>
+        <v>0.007025316455696202</v>
       </c>
       <c r="L50">
-        <v>0.7022900763358778</v>
+        <v>16.0126582278481</v>
       </c>
       <c r="M50">
-        <v>0.0009236641221374045</v>
+        <v>1.936708860759494</v>
       </c>
       <c r="N50">
-        <v>3.816793893129771E-05</v>
+        <v>0.00509493670886076</v>
       </c>
       <c r="O50">
-        <v>3.816793893129771E-05</v>
+        <v>3.164556962025317E-05</v>
       </c>
       <c r="P50">
-        <v>3.816793893129771E-05</v>
+        <v>3.797468354430379E-05</v>
       </c>
       <c r="Q50">
-        <v>0.01229007633587786</v>
+        <v>8.227848101265823E-05</v>
       </c>
       <c r="R50">
-        <v>0.003458015267175573</v>
+        <v>0.01234177215189873</v>
       </c>
       <c r="S50">
-        <v>1.908396946564886E-06</v>
+        <v>0.000569620253164557</v>
+      </c>
+      <c r="T50">
+        <v>0.0007721518987341771</v>
       </c>
     </row>
     <row r="51">
@@ -3838,67 +4088,72 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ross-Aplins</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>-19.30468</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AIMS-bridge</t>
+        </is>
       </c>
       <c r="E51">
-        <v>146.781019</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.395186</v>
+      </c>
+      <c r="F51">
+        <v>147.022964</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A78795</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>C12105</t>
-        </is>
-      </c>
-      <c r="I51">
-        <v>0.0002</v>
+          <t>A77325</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>C11790</t>
+        </is>
       </c>
       <c r="J51">
-        <v>0.00248</v>
+        <v>0.0002377622377622378</v>
       </c>
       <c r="K51">
-        <v>2.64</v>
+        <v>0.006321678321678322</v>
       </c>
       <c r="L51">
-        <v>0.6559999999999998</v>
+        <v>17.34265734265734</v>
       </c>
       <c r="M51">
-        <v>8.000000000000001E-05</v>
+        <v>2.027972027972028</v>
       </c>
       <c r="N51">
-        <v>4E-05</v>
+        <v>0.001342657342657343</v>
       </c>
       <c r="O51">
-        <v>8E-06</v>
+        <v>1.398601398601399E-05</v>
       </c>
       <c r="P51">
-        <v>4E-05</v>
+        <v>1.258741258741259E-05</v>
       </c>
       <c r="Q51">
-        <v>0.01152</v>
+        <v>3.216783216783217E-05</v>
       </c>
       <c r="R51">
-        <v>0.004192</v>
+        <v>0.01440559440559441</v>
       </c>
       <c r="S51">
-        <v>2E-06</v>
+        <v>0.0002671328671328671</v>
+      </c>
+      <c r="T51">
+        <v>3.076923076923077E-06</v>
       </c>
     </row>
     <row r="52">
@@ -3912,205 +4167,220 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Upstart-Mtink</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>-19.773321</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Cleveland-AlligatorCkSalt</t>
+        </is>
       </c>
       <c r="E52">
-        <v>147.515773</v>
-      </c>
-      <c r="F52" t="inlineStr">
+        <v>-19.362938</v>
+      </c>
+      <c r="F52">
+        <v>146.970421</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>A74844</t>
-        </is>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C12107</t>
-        </is>
-      </c>
-      <c r="I52">
-        <v>0.00015527950310559</v>
+          <t>A74840</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>C12201</t>
+        </is>
       </c>
       <c r="J52">
-        <v>0.002298136645962733</v>
+        <v>0.0004923599320882852</v>
       </c>
       <c r="K52">
-        <v>2.111801242236025</v>
+        <v>0.008200339558573855</v>
       </c>
       <c r="L52">
-        <v>0.5652173913043478</v>
+        <v>22.41086587436333</v>
       </c>
       <c r="M52">
-        <v>0.002670807453416149</v>
+        <v>2.937181663837012</v>
       </c>
       <c r="N52">
-        <v>3.105590062111801E-05</v>
+        <v>0.001398981324278438</v>
       </c>
       <c r="O52">
-        <v>2.484472049689441E-05</v>
+        <v>1.697792869269949E-05</v>
       </c>
       <c r="P52">
-        <v>8.695652173913041E-05</v>
+        <v>3.395585738539898E-06</v>
       </c>
       <c r="Q52">
-        <v>0.0131055900621118</v>
+        <v>4.414261460101868E-05</v>
       </c>
       <c r="R52">
-        <v>0.003465838509316769</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S52">
-        <v>1.552795031055901E-06</v>
+        <v>0.0004431239388794567</v>
+      </c>
+      <c r="T52">
+        <v>8.488964346349746E-07</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Burd-JeronaRd</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>-19.513845</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ross-mouth</t>
+        </is>
       </c>
       <c r="E53">
-        <v>147.218784</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.275335</v>
+      </c>
+      <c r="F53">
+        <v>146.830675</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>A74834</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C12121</t>
-        </is>
-      </c>
-      <c r="I53">
-        <v>0.0002573529411764706</v>
+          <t>A83990</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>C11782</t>
+        </is>
       </c>
       <c r="J53">
-        <v>0.0004591104734576758</v>
+        <v>0.0002452830188679245</v>
       </c>
       <c r="K53">
-        <v>23.25980392156863</v>
+        <v>0.007877358490566038</v>
       </c>
       <c r="L53">
-        <v>3.063725490196079</v>
+        <v>25.18867924528302</v>
       </c>
       <c r="M53">
-        <v>0.001941176470588235</v>
+        <v>2.94811320754717</v>
       </c>
       <c r="N53">
-        <v>4.901960784313726E-06</v>
+        <v>0.0008679245283018868</v>
       </c>
       <c r="O53">
-        <v>2.450980392156863E-06</v>
+        <v>2.358490566037736E-06</v>
       </c>
       <c r="P53">
-        <v>4.901960784313726E-06</v>
+        <v>5.188679245283019E-06</v>
       </c>
       <c r="Q53">
-        <v>0.002830188679245283</v>
+        <v>0.0001080188679245283</v>
       </c>
       <c r="R53">
-        <v>0.0003848039215686275</v>
+        <v>0.01820754716981132</v>
       </c>
       <c r="S53">
-        <v>8.333333333333334E-07</v>
+        <v>0.0001273584905660377</v>
+      </c>
+      <c r="T53">
+        <v>5.188679245283019E-07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AIMS-mouth</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>-19.300878</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Burd-mouth</t>
+        </is>
       </c>
       <c r="E54">
-        <v>147.043323</v>
-      </c>
-      <c r="F54" t="inlineStr">
+        <v>-19.663637</v>
+      </c>
+      <c r="F54">
+        <v>147.527879</v>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>A74827</t>
-        </is>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>C12127</t>
-        </is>
-      </c>
-      <c r="I54">
-        <v>0.0003875278396436525</v>
+          <t>A78794</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>C12139</t>
+        </is>
       </c>
       <c r="J54">
-        <v>0.008930957683741648</v>
+        <v>0.0003956043956043956</v>
       </c>
       <c r="K54">
-        <v>25.83518930957684</v>
+        <v>0.01027472527472527</v>
       </c>
       <c r="L54">
-        <v>3.207126948775056</v>
+        <v>26.20879120879121</v>
       </c>
       <c r="M54">
-        <v>0.0004031180400890868</v>
+        <v>3.192307692307693</v>
       </c>
       <c r="N54">
-        <v>1.11358574610245E-05</v>
+        <v>0.0002406593406593406</v>
       </c>
       <c r="O54">
-        <v>2.2271714922049E-06</v>
+        <v>2.747252747252747E-05</v>
       </c>
       <c r="P54">
-        <v>1.11358574610245E-05</v>
+        <v>5.494505494505494E-06</v>
       </c>
       <c r="Q54">
-        <v>0.002830188679245283</v>
+        <v>2.747252747252747E-05</v>
       </c>
       <c r="R54">
-        <v>2.427616926503341E-05</v>
+        <v>0.02071428571428571</v>
       </c>
       <c r="S54">
-        <v>3.630289532293986E-06</v>
+        <v>0.0003741758241758241</v>
+      </c>
+      <c r="T54">
+        <v>1.373626373626374E-06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4119,67 +4389,72 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Burd-mouth</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>-19.663637</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TSV-Bohle</t>
+        </is>
       </c>
       <c r="E55">
-        <v>147.527879</v>
-      </c>
-      <c r="F55" t="inlineStr">
+        <v>-19.25816</v>
+      </c>
+      <c r="F55">
+        <v>146.706871</v>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>A78794</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C12139</t>
-        </is>
-      </c>
-      <c r="I55">
-        <v>0.0003956043956043956</v>
+          <t>A74841</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>C12029</t>
+        </is>
       </c>
       <c r="J55">
-        <v>0.01027472527472527</v>
+        <v>0.000376425855513308</v>
       </c>
       <c r="K55">
-        <v>26.20879120879121</v>
+        <v>0.0004591104734576758</v>
       </c>
       <c r="L55">
-        <v>3.192307692307693</v>
+        <v>24.44866920152091</v>
       </c>
       <c r="M55">
-        <v>0.0002406593406593406</v>
+        <v>2.950570342205323</v>
       </c>
       <c r="N55">
-        <v>2.747252747252747E-05</v>
+        <v>0.001159695817490494</v>
       </c>
       <c r="O55">
-        <v>5.494505494505494E-06</v>
+        <v>7.604562737642585E-06</v>
       </c>
       <c r="P55">
-        <v>2.747252747252747E-05</v>
+        <v>1.520912547528517E-06</v>
       </c>
       <c r="Q55">
-        <v>0.02071428571428571</v>
+        <v>7.604562737642585E-06</v>
       </c>
       <c r="R55">
-        <v>0.0003741758241758241</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S55">
-        <v>1.373626373626374E-06</v>
+        <v>0.0005703422053231939</v>
+      </c>
+      <c r="T55">
+        <v>2.509505703422054E-06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4188,131 +4463,141 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TSV-StuartCk</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>-19.321821</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ross-mouth</t>
+        </is>
       </c>
       <c r="E56">
-        <v>146.837451</v>
-      </c>
-      <c r="F56" t="inlineStr">
+        <v>-19.275335</v>
+      </c>
+      <c r="F56">
+        <v>146.830675</v>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>wet</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>A77316</t>
-        </is>
-      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C12142</t>
-        </is>
-      </c>
-      <c r="I56">
-        <v>0.0002427184466019417</v>
+          <t>A74620</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>C11066</t>
+        </is>
       </c>
       <c r="J56">
-        <v>0.002330097087378641</v>
+        <v>0.0002681159420289855</v>
       </c>
       <c r="K56">
-        <v>0.9708737864077669</v>
+        <v>0.009094202898550724</v>
       </c>
       <c r="L56">
-        <v>0.3592233009708738</v>
+        <v>23.80434782608696</v>
       </c>
       <c r="M56">
-        <v>0.001718446601941748</v>
+        <v>3.097826086956522</v>
       </c>
       <c r="N56">
-        <v>4.854368932038835E-05</v>
+        <v>0.000133695652173913</v>
       </c>
       <c r="O56">
-        <v>0.0001941747572815534</v>
+        <v>1.811594202898551E-05</v>
       </c>
       <c r="P56">
-        <v>0.0001553398058252427</v>
+        <v>3.623188405797101E-06</v>
       </c>
       <c r="Q56">
-        <v>0.007407766990291262</v>
+        <v>7.173913043478262E-05</v>
       </c>
       <c r="R56">
-        <v>0.002456310679611651</v>
+        <v>0.01681159420289855</v>
       </c>
       <c r="S56">
-        <v>5.825242718446601E-06</v>
+        <v>0.000394927536231884</v>
+      </c>
+      <c r="T56">
+        <v>0.0003985507246376811</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>February</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ross-dam</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>-19.429937</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Haught-BarraCk</t>
+        </is>
       </c>
       <c r="E57">
-        <v>146.738035</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
+        <v>-19.479586</v>
+      </c>
+      <c r="F57">
+        <v>147.150848</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>A78786</t>
+          <t>wet</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>C12161</t>
-        </is>
-      </c>
-      <c r="I57">
-        <v>0.0004098360655737705</v>
+          <t>A74628</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>C11080</t>
+        </is>
       </c>
       <c r="J57">
-        <v>0.00459016393442623</v>
+        <v>0.0002533333333333333</v>
       </c>
       <c r="K57">
-        <v>2.459016393442623</v>
+        <v>0.009155555555555556</v>
       </c>
       <c r="L57">
-        <v>0.5409836065573771</v>
+        <v>22.84444444444444</v>
       </c>
       <c r="M57">
-        <v>0.0001967213114754098</v>
+        <v>3.008888888888889</v>
       </c>
       <c r="N57">
-        <v>8.19672131147541E-05</v>
+        <v>0.0004373333333333334</v>
       </c>
       <c r="O57">
-        <v>8.19672131147541E-05</v>
+        <v>2.222222222222222E-05</v>
       </c>
       <c r="P57">
-        <v>8.19672131147541E-05</v>
+        <v>9.777777777777779E-06</v>
       </c>
       <c r="Q57">
-        <v>0.0130327868852459</v>
+        <v>6.577777777777777E-05</v>
       </c>
       <c r="R57">
-        <v>0.007967213114754099</v>
+        <v>0.01671111111111111</v>
       </c>
       <c r="S57">
-        <v>4.098360655737705E-06</v>
+        <v>0.0004488888888888889</v>
+      </c>
+      <c r="T57">
+        <v>0.0005511111111111112</v>
       </c>
     </row>
     <row r="58">
@@ -4321,67 +4606,72 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Haught-Giru</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>-19.512679</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Burd-JeronaRd</t>
+        </is>
       </c>
       <c r="E58">
-        <v>147.112332</v>
-      </c>
-      <c r="F58" t="inlineStr">
+        <v>-19.513845</v>
+      </c>
+      <c r="F58">
+        <v>147.218784</v>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>A74839</t>
-        </is>
-      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C12166</t>
-        </is>
-      </c>
-      <c r="I58">
-        <v>0.0001908396946564885</v>
+          <t>A74834</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>C12121</t>
+        </is>
       </c>
       <c r="J58">
-        <v>0.001679389312977099</v>
+        <v>0.0002573529411764706</v>
       </c>
       <c r="K58">
-        <v>1.984732824427481</v>
+        <v>0.0004591104734576758</v>
       </c>
       <c r="L58">
-        <v>0.5114503816793894</v>
+        <v>23.25980392156863</v>
       </c>
       <c r="M58">
-        <v>0.0001297709923664122</v>
+        <v>3.063725490196079</v>
       </c>
       <c r="N58">
-        <v>3.816793893129771E-05</v>
+        <v>0.001941176470588235</v>
       </c>
       <c r="O58">
-        <v>3.053435114503817E-05</v>
+        <v>4.901960784313726E-06</v>
       </c>
       <c r="P58">
-        <v>3.816793893129771E-05</v>
+        <v>2.450980392156863E-06</v>
       </c>
       <c r="Q58">
-        <v>0.009618320610687023</v>
+        <v>4.901960784313726E-06</v>
       </c>
       <c r="R58">
-        <v>0.00333587786259542</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S58">
-        <v>1.908396946564886E-06</v>
+        <v>0.0003848039215686275</v>
+      </c>
+      <c r="T58">
+        <v>8.333333333333334E-07</v>
       </c>
     </row>
     <row r="59">
@@ -4390,141 +4680,151 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TSV-StuartCk</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>-19.321821</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AIMS-mouth</t>
+        </is>
       </c>
       <c r="E59">
-        <v>146.837451</v>
-      </c>
-      <c r="F59" t="inlineStr">
+        <v>-19.300878</v>
+      </c>
+      <c r="F59">
+        <v>147.043323</v>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>A74820</t>
-        </is>
-      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>C12167</t>
-        </is>
-      </c>
-      <c r="I59">
-        <v>3.586800573888092E-05</v>
+          <t>A74827</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C12127</t>
+        </is>
       </c>
       <c r="J59">
-        <v>0.0004591104734576758</v>
+        <v>0.0003875278396436525</v>
       </c>
       <c r="K59">
-        <v>1.822094691535151</v>
+        <v>0.008930957683741648</v>
       </c>
       <c r="L59">
-        <v>0.5796269727403156</v>
+        <v>25.83518930957684</v>
       </c>
       <c r="M59">
-        <v>0.004433285509325682</v>
+        <v>3.207126948775056</v>
       </c>
       <c r="N59">
-        <v>7.173601147776184E-06</v>
+        <v>0.0004031180400890868</v>
       </c>
       <c r="O59">
-        <v>1.434720229555237E-06</v>
+        <v>1.11358574610245E-05</v>
       </c>
       <c r="P59">
-        <v>7.173601147776184E-06</v>
+        <v>2.2271714922049E-06</v>
       </c>
       <c r="Q59">
-        <v>0.005523672883787661</v>
+        <v>1.11358574610245E-05</v>
       </c>
       <c r="R59">
-        <v>0.001352941176470588</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S59">
-        <v>3.586800573888092E-07</v>
+        <v>2.427616926503341E-05</v>
+      </c>
+      <c r="T59">
+        <v>3.630289532293986E-06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>June</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Haught-ReedBeds</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>-19.499366</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Cleveland-CrocCk</t>
+        </is>
       </c>
       <c r="E60">
-        <v>147.05127</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.387241</v>
+      </c>
+      <c r="F60">
+        <v>147.014767</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>A83991</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>C12173</t>
-        </is>
-      </c>
-      <c r="I60">
-        <v>0.0002717391304347826</v>
+          <t>A74826</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>C12028</t>
+        </is>
       </c>
       <c r="J60">
-        <v>0.0025</v>
+        <v>0.0002872727272727273</v>
       </c>
       <c r="K60">
-        <v>1.739130434782609</v>
+        <v>0.005890909090909091</v>
       </c>
       <c r="L60">
-        <v>0.5108695652173914</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="M60">
-        <v>0.03695652173913044</v>
+        <v>3.309090909090909</v>
       </c>
       <c r="N60">
-        <v>0.0001195652173913044</v>
+        <v>0.0006036363636363636</v>
       </c>
       <c r="O60">
-        <v>7.608695652173912E-05</v>
+        <v>9.090909090909091E-06</v>
       </c>
       <c r="P60">
-        <v>0.0002282608695652174</v>
+        <v>1.818181818181818E-06</v>
       </c>
       <c r="Q60">
-        <v>0.008793478260869566</v>
+        <v>9.090909090909091E-06</v>
       </c>
       <c r="R60">
-        <v>0.002706521739130435</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S60">
-        <v>2.717391304347826E-06</v>
+        <v>0.0001745454545454545</v>
+      </c>
+      <c r="T60">
+        <v>1.963636363636364E-06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4533,67 +4833,72 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TSV-Bluewater</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>-19.176311</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ross-mouth</t>
+        </is>
       </c>
       <c r="E61">
-        <v>146.552749</v>
-      </c>
-      <c r="F61" t="inlineStr">
+        <v>-19.275335</v>
+      </c>
+      <c r="F61">
+        <v>146.830675</v>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>A74823</t>
-        </is>
-      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C12174</t>
-        </is>
-      </c>
-      <c r="I61">
-        <v>0.001388888888888889</v>
+          <t>A78789</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C12188</t>
+        </is>
       </c>
       <c r="J61">
-        <v>0.01</v>
+        <v>0.0005239234449760765</v>
       </c>
       <c r="K61">
-        <v>6.666666666666666</v>
+        <v>0.01177033492822967</v>
       </c>
       <c r="L61">
-        <v>0.5555555555555556</v>
+        <v>29.1866028708134</v>
       </c>
       <c r="M61">
-        <v>0.005722222222222222</v>
+        <v>3.349282296650718</v>
       </c>
       <c r="N61">
-        <v>0.0002777777777777778</v>
+        <v>3.588516746411483E-05</v>
       </c>
       <c r="O61">
-        <v>0.0001111111111111111</v>
+        <v>2.392344497607656E-05</v>
       </c>
       <c r="P61">
-        <v>0.0002777777777777778</v>
+        <v>4.784688995215311E-06</v>
       </c>
       <c r="Q61">
-        <v>0.009722222222222222</v>
+        <v>2.392344497607656E-05</v>
       </c>
       <c r="R61">
-        <v>0.002666666666666667</v>
+        <v>0.0211244019138756</v>
       </c>
       <c r="S61">
-        <v>4.444444444444445E-05</v>
+        <v>4.282296650717703E-05</v>
+      </c>
+      <c r="T61">
+        <v>1.196172248803828E-06</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -4602,67 +4907,72 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Burd-irrig</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>-19.58904</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Haught-Heatleys</t>
+        </is>
       </c>
       <c r="E62">
-        <v>147.397985</v>
-      </c>
-      <c r="F62" t="inlineStr">
+        <v>-19.516906</v>
+      </c>
+      <c r="F62">
+        <v>147.045995</v>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>A78787</t>
-        </is>
-      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>C12186</t>
-        </is>
-      </c>
-      <c r="I62">
-        <v>0.0002192982456140351</v>
+          <t>A74697</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C11042</t>
+        </is>
       </c>
       <c r="J62">
-        <v>0.003245614035087719</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K62">
-        <v>1.666666666666667</v>
+        <v>0.002159090909090909</v>
       </c>
       <c r="L62">
-        <v>0.6929824561403509</v>
+        <v>1.988636363636364</v>
       </c>
       <c r="M62">
-        <v>0.0002017543859649123</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="N62">
-        <v>4.385964912280701E-05</v>
+        <v>3.409090909090909E-05</v>
       </c>
       <c r="O62">
-        <v>7.894736842105263E-05</v>
+        <v>2.840909090909091E-05</v>
       </c>
       <c r="P62">
-        <v>4.385964912280701E-05</v>
+        <v>5.681818181818182E-06</v>
       </c>
       <c r="Q62">
-        <v>0.01228070175438596</v>
+        <v>0.0001534090909090909</v>
       </c>
       <c r="R62">
-        <v>0.003657894736842106</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="S62">
-        <v>2.192982456140351E-06</v>
+        <v>0.002818181818181818</v>
+      </c>
+      <c r="T62">
+        <v>1.420454545454546E-06</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -4671,67 +4981,72 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ross-mouth</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>-19.275335</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Haught-mouth</t>
+        </is>
       </c>
       <c r="E63">
-        <v>146.830675</v>
-      </c>
-      <c r="F63" t="inlineStr">
+        <v>-19.411312</v>
+      </c>
+      <c r="F63">
+        <v>147.116264</v>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>A78789</t>
-        </is>
-      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C12188</t>
-        </is>
-      </c>
-      <c r="I63">
-        <v>0.0005239234449760765</v>
+          <t>A74702</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>C11061</t>
+        </is>
       </c>
       <c r="J63">
-        <v>0.01177033492822967</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K63">
-        <v>29.1866028708134</v>
+        <v>0.009782135076252724</v>
       </c>
       <c r="L63">
-        <v>3.349282296650718</v>
+        <v>23.31154684095861</v>
       </c>
       <c r="M63">
-        <v>3.588516746411483E-05</v>
+        <v>3.18082788671024</v>
       </c>
       <c r="N63">
-        <v>2.392344497607656E-05</v>
+        <v>1.982570806100218E-05</v>
       </c>
       <c r="O63">
-        <v>4.784688995215311E-06</v>
+        <v>1.089324618736383E-05</v>
       </c>
       <c r="P63">
-        <v>2.392344497607656E-05</v>
+        <v>2.178649237472767E-06</v>
       </c>
       <c r="Q63">
-        <v>0.0211244019138756</v>
+        <v>8.278867102396513E-06</v>
       </c>
       <c r="R63">
-        <v>4.282296650717703E-05</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S63">
-        <v>1.196172248803828E-06</v>
+        <v>1.655773420479303E-05</v>
+      </c>
+      <c r="T63">
+        <v>8.278867102396515E-07</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4740,67 +5055,72 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ross-dam</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>-19.429937</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ross-Aplins</t>
+        </is>
       </c>
       <c r="E64">
-        <v>146.738035</v>
-      </c>
-      <c r="F64" t="inlineStr">
+        <v>-19.30468</v>
+      </c>
+      <c r="F64">
+        <v>146.781019</v>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>A74828</t>
-        </is>
-      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>C12193</t>
-        </is>
-      </c>
-      <c r="I64">
-        <v>0.0004464285714285714</v>
+          <t>A74684</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>C11074</t>
+        </is>
       </c>
       <c r="J64">
-        <v>0.0025</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K64">
-        <v>1.607142857142857</v>
+        <v>0.001608040201005025</v>
       </c>
       <c r="L64">
-        <v>0.4285714285714286</v>
+        <v>1.85929648241206</v>
       </c>
       <c r="M64">
-        <v>0.0006428571428571428</v>
+        <v>0.4673366834170855</v>
       </c>
       <c r="N64">
-        <v>8.928571428571429E-05</v>
+        <v>0.0001206030150753769</v>
       </c>
       <c r="O64">
-        <v>8.928571428571429E-05</v>
+        <v>2.512562814070352E-05</v>
       </c>
       <c r="P64">
-        <v>8.928571428571429E-05</v>
+        <v>2.010050251256282E-05</v>
       </c>
       <c r="Q64">
-        <v>0.006339285714285714</v>
+        <v>0.0001105527638190955</v>
       </c>
       <c r="R64">
-        <v>0.003589285714285715</v>
+        <v>0.006834170854271356</v>
       </c>
       <c r="S64">
-        <v>4.464285714285715E-06</v>
+        <v>0.002688442211055276</v>
+      </c>
+      <c r="T64">
+        <v>1.256281407035176E-06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4809,269 +5129,289 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Burd-Lillismere</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>-19.518036</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ross-mouth</t>
+        </is>
       </c>
       <c r="E65">
-        <v>147.419893</v>
-      </c>
-      <c r="F65" t="inlineStr">
+        <v>-19.275335</v>
+      </c>
+      <c r="F65">
+        <v>146.830675</v>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>A74832</t>
-        </is>
-      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C12194</t>
-        </is>
-      </c>
-      <c r="I65">
-        <v>0.0002032520325203252</v>
+          <t>A74699</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C11106</t>
+        </is>
       </c>
       <c r="J65">
-        <v>0.002195121951219512</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K65">
-        <v>2.113821138211382</v>
+        <v>0.009449152542372882</v>
       </c>
       <c r="L65">
-        <v>0.6910569105691057</v>
+        <v>23.51694915254237</v>
       </c>
       <c r="M65">
-        <v>7.317073170731707E-05</v>
+        <v>3.199152542372881</v>
       </c>
       <c r="N65">
-        <v>4.065040650406504E-05</v>
+        <v>1.016949152542373E-05</v>
       </c>
       <c r="O65">
-        <v>4.065040650406504E-05</v>
+        <v>1.059322033898305E-05</v>
       </c>
       <c r="P65">
-        <v>4.065040650406504E-05</v>
+        <v>1.059322033898305E-06</v>
       </c>
       <c r="Q65">
-        <v>0.007195121951219513</v>
+        <v>4.661016949152542E-06</v>
       </c>
       <c r="R65">
-        <v>0.002170731707317073</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S65">
-        <v>2.032520325203252E-06</v>
+        <v>1.652542372881356E-05</v>
+      </c>
+      <c r="T65">
+        <v>2.288135593220339E-06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Haught-Crooked</t>
-        </is>
-      </c>
-      <c r="D66">
-        <v>-19.517772</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ross-Blacks</t>
+        </is>
       </c>
       <c r="E66">
-        <v>147.090193</v>
-      </c>
-      <c r="F66" t="inlineStr">
+        <v>-19.34905</v>
+      </c>
+      <c r="F66">
+        <v>146.73166</v>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>A74838</t>
-        </is>
-      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C12199</t>
-        </is>
-      </c>
-      <c r="I66">
-        <v>9.025270758122743E-05</v>
+          <t>A74701</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>C11123</t>
+        </is>
       </c>
       <c r="J66">
-        <v>0.002779783393501805</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K66">
-        <v>5.270758122743683</v>
+        <v>0.002113821138211382</v>
       </c>
       <c r="L66">
-        <v>0.6714801444043322</v>
+        <v>2.439024390243902</v>
       </c>
       <c r="M66">
-        <v>0.002379061371841156</v>
+        <v>0.4471544715447154</v>
       </c>
       <c r="N66">
-        <v>1.805054151624549E-05</v>
+        <v>0.0002926829268292683</v>
       </c>
       <c r="O66">
-        <v>2.166064981949458E-05</v>
+        <v>4.065040650406504E-05</v>
       </c>
       <c r="P66">
-        <v>1.805054151624549E-05</v>
+        <v>2.439024390243902E-05</v>
       </c>
       <c r="Q66">
-        <v>0.008555956678700362</v>
+        <v>0.0002439024390243902</v>
       </c>
       <c r="R66">
-        <v>0.001613718411552347</v>
+        <v>0.007626016260162602</v>
       </c>
       <c r="S66">
-        <v>9.025270758122744E-07</v>
+        <v>0.002804878048780488</v>
+      </c>
+      <c r="T66">
+        <v>2.032520325203252E-06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TSV-Bohle</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>-19.25816</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Burd-mouth</t>
+        </is>
       </c>
       <c r="E67">
-        <v>146.706871</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>wet</t>
-        </is>
+        <v>-19.663637</v>
+      </c>
+      <c r="F67">
+        <v>147.527879</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>A77327</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C12200</t>
-        </is>
-      </c>
-      <c r="I67">
-        <v>0.00078125</v>
+          <t>A74689</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>C11132</t>
+        </is>
       </c>
       <c r="J67">
-        <v>0.005</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K67">
-        <v>2.1875</v>
+        <v>0.009291553133514987</v>
       </c>
       <c r="L67">
-        <v>0.40625</v>
+        <v>23.97820163487738</v>
       </c>
       <c r="M67">
-        <v>0.00309375</v>
+        <v>3.160762942779292</v>
       </c>
       <c r="N67">
-        <v>0.00015625</v>
+        <v>2.452316076294278E-05</v>
       </c>
       <c r="O67">
-        <v>0.00040625</v>
+        <v>1.362397820163488E-05</v>
       </c>
       <c r="P67">
-        <v>0.0006875000000000001</v>
+        <v>1.08991825613079E-06</v>
       </c>
       <c r="Q67">
-        <v>0.00928125</v>
+        <v>4.904632152588556E-06</v>
       </c>
       <c r="R67">
-        <v>0.008375</v>
+        <v>0.002830188679245283</v>
       </c>
       <c r="S67">
-        <v>5.3125E-05</v>
+        <v>0.0001839237057220708</v>
+      </c>
+      <c r="T67">
+        <v>8.719346049046322E-07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>November</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland-AlligatorCkSalt</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>-19.362938</v>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Haught-Giru</t>
+        </is>
       </c>
       <c r="E68">
-        <v>146.970421</v>
-      </c>
-      <c r="F68" t="inlineStr">
+        <v>-19.512679</v>
+      </c>
+      <c r="F68">
+        <v>147.112332</v>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>dry</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>A74840</t>
-        </is>
-      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>C12201</t>
-        </is>
-      </c>
-      <c r="I68">
-        <v>0.0004923599320882852</v>
+          <t>A74700</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>C11167</t>
+        </is>
       </c>
       <c r="J68">
-        <v>0.008200339558573855</v>
+        <v>3.586800573888092E-05</v>
       </c>
       <c r="K68">
-        <v>22.41086587436333</v>
+        <v>0.002846153846153846</v>
       </c>
       <c r="L68">
-        <v>2.937181663837012</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="M68">
-        <v>0.001398981324278438</v>
+        <v>0.7923076923076924</v>
       </c>
       <c r="N68">
-        <v>1.697792869269949E-05</v>
+        <v>0.0001384615384615385</v>
       </c>
       <c r="O68">
-        <v>3.395585738539898E-06</v>
+        <v>3.846153846153846E-05</v>
       </c>
       <c r="P68">
-        <v>4.414261460101868E-05</v>
+        <v>4.615384615384615E-05</v>
       </c>
       <c r="Q68">
-        <v>0.002830188679245283</v>
+        <v>0.0003384615384615385</v>
       </c>
       <c r="R68">
-        <v>0.0004431239388794567</v>
+        <v>0.01053846153846154</v>
       </c>
       <c r="S68">
-        <v>8.488964346349746E-07</v>
+        <v>0.002476923076923077</v>
+      </c>
+      <c r="T68">
+        <v>1.538461538461538E-05</v>
       </c>
     </row>
   </sheetData>
